--- a/BELGRANO 1646/Septiembre/Septiembre-BLG1646.xlsx
+++ b/BELGRANO 1646/Septiembre/Septiembre-BLG1646.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BELGRANO 1646\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BELGRANO 1646\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB5E82F-4BB9-49A0-AD02-115059E05FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA439A5-1ACE-456C-A8FC-162662133267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$127</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$122</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="174">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -490,15 +490,9 @@
     <t>Articulos de limpieza - Montoya Alejandra</t>
   </si>
   <si>
-    <t>Limpieza de SUM - Sra. Monica</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sr. Diego Britez </t>
   </si>
   <si>
-    <t xml:space="preserve">Compra de materiales </t>
-  </si>
-  <si>
     <t>EL MES ANTERIOR ATILIO QUEDO CON UN SALDO A FAVOR DE:</t>
   </si>
   <si>
@@ -526,57 +520,9 @@
     <t>YA ABONO:</t>
   </si>
   <si>
-    <t>Salvatierra Matias - Desobstruccion y limpieza de canaletas guardaganado en pluviales de cochera en 1 piso, 2 piso y coletora de pluvial</t>
-  </si>
-  <si>
-    <t>Salvatierra Matias - Desobstruccion columna en baño 7B</t>
-  </si>
-  <si>
-    <t>Salvatierra Matias -Servicio de diagnostico por imágenes en 6B - Cuota 1/2</t>
-  </si>
-  <si>
-    <t>Fumigacion 19/08</t>
-  </si>
-  <si>
-    <t>Contessi - Provision y cambio de lapices de nivelacion en el montaauto</t>
-  </si>
-  <si>
-    <t>Pago mis cuentas 07/08</t>
-  </si>
-  <si>
-    <t>Debito 12/08</t>
-  </si>
-  <si>
-    <t>SEGURO OBLIGATORIO SR DIEGO BRITEZ FEDERACION PATRONAL DEBITO AUTOMATICO 01/08</t>
-  </si>
-  <si>
-    <t>Numero 1859135 Debito automatico 01/08</t>
-  </si>
-  <si>
-    <t>Pintureria prestigio - Compra de pintura lockson larga duracion - 12/08</t>
-  </si>
-  <si>
-    <t>Pintureria prestigio - Compra de pintura lockson larga duracion - 08/08</t>
-  </si>
-  <si>
-    <t>Efectivo</t>
-  </si>
-  <si>
-    <t>Debito 29/08</t>
-  </si>
-  <si>
-    <t>Pinsur - Colmeiro Oscar - Sellado de mamposteria e inyectado con terminacion de pintura de los frentes de balcones lado izquiero - Transferencia y efectivo</t>
-  </si>
-  <si>
-    <t>Pinsur - Colmeiro Oscar - Vaciado de agua en parantes, ajuste de tornillos y sellados - Transferencia y efectivo</t>
-  </si>
-  <si>
     <t>GASTOS PARTICULARES</t>
   </si>
   <si>
-    <t>No hubo boleta</t>
-  </si>
-  <si>
     <t>VTO: 15/10</t>
   </si>
   <si>
@@ -586,28 +532,58 @@
     <t>Honorarios SEPTIEMBRE</t>
   </si>
   <si>
-    <t>Energoup MES DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGOSTO Dadona - Arreglo piso 5to </t>
-  </si>
-  <si>
     <t>Ingreso mes de AGOSTO</t>
   </si>
   <si>
     <t>Servisur - programacion de relojes</t>
   </si>
   <si>
-    <t xml:space="preserve">Rohe </t>
-  </si>
-  <si>
     <t>Servisur - plafones led de 12W en escaleras y pallieres - Sensor de movimiento escalera piso 5</t>
   </si>
   <si>
     <t xml:space="preserve">Casa Ruan - 14 plafones led y un sensor </t>
   </si>
   <si>
-    <t>Salvatierra Matias - Servicio de diagnostico por imágenes en 6B - Cuota 1 de 2</t>
+    <t xml:space="preserve">Prestigio - compra de Loxon Color </t>
+  </si>
+  <si>
+    <t>Salvatierra Matias -Servicio de diagnostico por imágenes en 6B - Cuota 2/2</t>
+  </si>
+  <si>
+    <t>SEGURO OBLIGATORIO SR DIEGO BRITEZ FEDERACION PATRONAL DEBITO AUTOMATICO 04/09</t>
+  </si>
+  <si>
+    <t>Numero 1859135 Debito automatico 01/09</t>
+  </si>
+  <si>
+    <t>Debito 02/09</t>
+  </si>
+  <si>
+    <t>Pago mis cuentas 05/09</t>
+  </si>
+  <si>
+    <t>Debito 12/09</t>
+  </si>
+  <si>
+    <t>Debito 23/09</t>
+  </si>
+  <si>
+    <t>Fumigacion 29/09</t>
+  </si>
+  <si>
+    <t>Mano de obra y materiales trabajo en UF 28 - Por ruidos molestos</t>
+  </si>
+  <si>
+    <t>Rohe - Envio de ceramicas</t>
+  </si>
+  <si>
+    <t>Rohe - Compra de ceramicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leonardo Balcazza - Sellado de balcon parte de losa, salida carpinteria mecanica, sellado de fisuras entre union de olsas y pared -  Aplicación de tapagoteras SIKA UF 43 </t>
+  </si>
+  <si>
+    <t>Energroup</t>
   </si>
 </sst>
 </file>
@@ -1336,7 +1312,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="249">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
@@ -1554,7 +1530,6 @@
     <xf numFmtId="44" fontId="2" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1596,9 +1571,6 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1617,12 +1589,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1697,6 +1663,18 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1727,21 +1705,9 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1766,12 +1732,23 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="20" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2137,24 +2114,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P137"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P132"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="18.33203125" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8"/>
       <c r="B1" s="97" t="s">
         <v>118</v>
@@ -2163,7 +2140,7 @@
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="64"/>
       <c r="B2" s="65" t="s">
         <v>0</v>
@@ -2172,7 +2149,7 @@
       <c r="D2" s="65"/>
       <c r="E2" s="66"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="67"/>
       <c r="B3" s="68" t="s">
         <v>88</v>
@@ -2181,7 +2158,7 @@
       <c r="D3" s="68"/>
       <c r="E3" s="69"/>
     </row>
-    <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="67"/>
       <c r="B4" s="68" t="s">
         <v>89</v>
@@ -2190,20 +2167,20 @@
       <c r="D4" s="68"/>
       <c r="E4" s="69"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="C5" s="71" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D5" s="71"/>
       <c r="E5" s="72"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="67" t="s">
         <v>99</v>
       </c>
@@ -2212,7 +2189,7 @@
       <c r="D6" s="68"/>
       <c r="E6" s="69"/>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="70" t="s">
         <v>98</v>
       </c>
@@ -2221,125 +2198,125 @@
       <c r="D7" s="71"/>
       <c r="E7" s="72"/>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="200" t="s">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="196" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="201"/>
-      <c r="D14" s="202"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="203"/>
-      <c r="C15" s="204"/>
-      <c r="D15" s="205"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="203"/>
-      <c r="C16" s="204"/>
-      <c r="D16" s="205"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="206"/>
-      <c r="C17" s="207"/>
-      <c r="D17" s="208"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C14" s="197"/>
+      <c r="D14" s="198"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="199"/>
+      <c r="C15" s="200"/>
+      <c r="D15" s="201"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="199"/>
+      <c r="C16" s="200"/>
+      <c r="D16" s="201"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="202"/>
+      <c r="C17" s="203"/>
+      <c r="D17" s="204"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="61" t="s">
         <v>86</v>
       </c>
       <c r="B21" s="62"/>
       <c r="C21" s="63"/>
       <c r="D21" s="59"/>
-      <c r="E21" s="188" t="s">
+      <c r="E21" s="186" t="s">
         <v>121</v>
       </c>
-      <c r="F21" s="189" t="s">
+      <c r="F21" s="187" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="120" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="129"/>
-      <c r="E22" s="187"/>
-      <c r="F22" s="187"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E22" s="185"/>
+      <c r="F22" s="185"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="120" t="s">
         <v>126</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="173">
-        <v>1277708.7</v>
+      <c r="D23" s="172">
+        <v>1356359.4</v>
       </c>
       <c r="E23" s="133">
         <f>D23*91.91%</f>
-        <v>1174342.0661699998</v>
+        <v>1246629.9245399998</v>
       </c>
       <c r="F23" s="133">
         <f>D23*8.09%</f>
-        <v>103366.63382999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+        <v>109729.47545999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="120" t="s">
         <v>2</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="173">
-        <v>-277901.65000000002</v>
+      <c r="D24" s="172">
+        <v>-295008.15999999997</v>
       </c>
       <c r="E24" s="133">
         <f t="shared" ref="E24:E25" si="0">D24*91.91%</f>
-        <v>-255419.40651500001</v>
+        <v>-271141.99985599995</v>
       </c>
       <c r="F24" s="133">
         <f t="shared" ref="F24:F25" si="1">D24*8.09%</f>
-        <v>-22482.243485000003</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+        <v>-23866.160143999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="120" t="s">
         <v>112</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="173">
-        <v>0.95</v>
+      <c r="D25" s="172">
+        <v>0.76</v>
       </c>
       <c r="E25" s="133">
         <f t="shared" si="0"/>
-        <v>0.87314499999999984</v>
+        <v>0.69851599999999991</v>
       </c>
       <c r="F25" s="133">
         <f t="shared" si="1"/>
-        <v>7.6854999999999993E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+        <v>6.1484000000000004E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="120"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="173"/>
+      <c r="D26" s="172"/>
       <c r="E26" s="133"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="95" t="s">
         <v>3</v>
       </c>
@@ -2347,32 +2324,32 @@
       <c r="C27" s="95"/>
       <c r="D27" s="107">
         <f>SUM(D23:D26)</f>
-        <v>999807.99999999988</v>
+        <v>1061352</v>
       </c>
       <c r="E27" s="107">
         <f>SUM(E23:E26)</f>
-        <v>918923.5327999997</v>
+        <v>975488.6231999998</v>
       </c>
       <c r="F27" s="107">
         <f>SUM(F23:F26)</f>
-        <v>80884.467199999999</v>
+        <v>85863.376799999998</v>
       </c>
       <c r="G27" s="108">
         <f>E27+F27</f>
-        <v>999807.99999999965</v>
+        <v>1061351.9999999998</v>
       </c>
       <c r="H27" s="146" t="str">
         <f>IF(D27=G27, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="94" t="s">
         <v>109</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="174">
+      <c r="D28" s="173">
         <v>0</v>
       </c>
       <c r="E28" s="133">
@@ -2385,11 +2362,11 @@
       </c>
       <c r="H28" s="146"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="94"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="173">
+      <c r="D29" s="172">
         <v>0</v>
       </c>
       <c r="E29" s="133">
@@ -2402,25 +2379,25 @@
       </c>
       <c r="H29" s="146"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="94"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="173"/>
+      <c r="D30" s="172"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="H30" s="146"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="94"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="173"/>
+      <c r="D31" s="172"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="H31" s="146"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="95" t="s">
         <v>117</v>
       </c>
@@ -2447,13 +2424,13 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="94" t="s">
         <v>109</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="174"/>
+      <c r="D33" s="173"/>
       <c r="E33" s="133">
         <f>D33*91.91%</f>
         <v>0</v>
@@ -2464,13 +2441,13 @@
       </c>
       <c r="H33" s="146"/>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>130</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="173"/>
+      <c r="D34" s="172"/>
       <c r="E34" s="133">
         <f t="shared" ref="E34:E35" si="3">D34*91.91%</f>
         <v>0</v>
@@ -2481,13 +2458,13 @@
       </c>
       <c r="H34" s="146"/>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="94" t="s">
         <v>2</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="173"/>
+      <c r="D35" s="172"/>
       <c r="E35" s="133">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2498,7 +2475,7 @@
       </c>
       <c r="H35" s="146"/>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="95" t="s">
         <v>110</v>
       </c>
@@ -2518,34 +2495,34 @@
       </c>
       <c r="H36" s="146"/>
     </row>
-    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="128"/>
       <c r="B37" s="98"/>
       <c r="C37" s="98"/>
-      <c r="D37" s="173"/>
+      <c r="D37" s="172"/>
       <c r="E37" s="119"/>
       <c r="F37" s="119"/>
       <c r="H37" s="146"/>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="128"/>
       <c r="B38" s="98"/>
       <c r="C38" s="98"/>
-      <c r="D38" s="173"/>
+      <c r="D38" s="172"/>
       <c r="E38" s="119"/>
       <c r="F38" s="119"/>
       <c r="H38" s="146"/>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="98"/>
       <c r="B39" s="98"/>
       <c r="C39" s="110"/>
-      <c r="D39" s="173"/>
+      <c r="D39" s="172"/>
       <c r="E39" s="119"/>
       <c r="F39" s="119"/>
       <c r="H39" s="146"/>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="95" t="s">
         <v>117</v>
       </c>
@@ -2562,7 +2539,7 @@
       </c>
       <c r="H40" s="146"/>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="94"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -2577,7 +2554,7 @@
       </c>
       <c r="H41" s="146"/>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="94"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -2592,11 +2569,11 @@
       </c>
       <c r="H42" s="146"/>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="94"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="176"/>
+      <c r="D43" s="175"/>
       <c r="E43" s="133">
         <f>D43*91.91%</f>
         <v>0</v>
@@ -2607,7 +2584,7 @@
       </c>
       <c r="H43" s="146"/>
     </row>
-    <row r="44" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="95" t="s">
         <v>127</v>
       </c>
@@ -2621,7 +2598,7 @@
         <f>SUM(E41:E43)</f>
         <v>0</v>
       </c>
-      <c r="F44" s="163">
+      <c r="F44" s="162">
         <f>SUM(F41:F43)</f>
         <v>0</v>
       </c>
@@ -2631,20 +2608,20 @@
       </c>
       <c r="H44" s="146"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="94" t="s">
         <v>4</v>
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="176"/>
+      <c r="D45" s="175"/>
       <c r="E45" s="113"/>
       <c r="F45" s="100"/>
       <c r="H45" s="146"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="94" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="98"/>
@@ -2661,15 +2638,15 @@
       </c>
       <c r="H46" s="146"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="94" t="s">
         <v>5</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C47" s="7"/>
-      <c r="D47" s="245">
+      <c r="D47" s="112">
         <f>6338.54+57496.89+108023.08</f>
         <v>171858.51</v>
       </c>
@@ -2683,15 +2660,15 @@
       </c>
       <c r="H47" s="146"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="94" t="s">
         <v>135</v>
       </c>
       <c r="B48" s="98" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C48" s="7"/>
-      <c r="D48" s="183">
+      <c r="D48" s="112">
         <v>565971.80000000005</v>
       </c>
       <c r="E48" s="133">
@@ -2704,7 +2681,7 @@
       </c>
       <c r="H48" s="146"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="95" t="s">
         <v>6</v>
       </c>
@@ -2731,49 +2708,45 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="176"/>
+      <c r="D50" s="175"/>
       <c r="E50" s="114"/>
       <c r="F50" s="7"/>
       <c r="H50" s="146"/>
     </row>
-    <row r="51" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="180" t="s">
-        <v>158</v>
-      </c>
-      <c r="B51" s="169"/>
-      <c r="C51" s="170"/>
-      <c r="D51" s="176">
-        <v>160000</v>
-      </c>
+    <row r="51" spans="1:16" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="179"/>
+      <c r="B51" s="168"/>
+      <c r="C51" s="169"/>
+      <c r="D51" s="175"/>
       <c r="E51" s="145">
         <f>D51</f>
-        <v>160000</v>
+        <v>0</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="108">
         <f>D51</f>
-        <v>160000</v>
+        <v>0</v>
       </c>
       <c r="H51" s="156">
         <f>E51+F51</f>
-        <v>160000</v>
-      </c>
-      <c r="I51" s="171"/>
-      <c r="J51" s="171"/>
-    </row>
-    <row r="52" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="180" t="s">
+        <v>0</v>
+      </c>
+      <c r="I51" s="170"/>
+      <c r="J51" s="170"/>
+    </row>
+    <row r="52" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="179" t="s">
         <v>138</v>
       </c>
-      <c r="B52" s="169"/>
-      <c r="C52" s="170"/>
-      <c r="D52" s="183">
+      <c r="B52" s="168"/>
+      <c r="C52" s="169"/>
+      <c r="D52" s="112">
         <v>372000</v>
       </c>
       <c r="E52" s="145">
@@ -2789,80 +2762,80 @@
         <f>E52+F52</f>
         <v>372000</v>
       </c>
-      <c r="I52" s="171">
+      <c r="I52" s="170">
         <f>H52-D52</f>
         <v>0</v>
       </c>
-      <c r="J52" s="171"/>
-    </row>
-    <row r="53" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J52" s="170"/>
+    </row>
+    <row r="53" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="B53" s="158"/>
+      <c r="B53" s="157"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="183">
-        <v>127113.12</v>
+      <c r="D53" s="112">
+        <v>153807</v>
       </c>
       <c r="E53" s="145">
         <f t="shared" ref="E53:E57" si="7">D53*91.91%</f>
-        <v>116829.66859199999</v>
+        <v>141364.01369999998</v>
       </c>
       <c r="F53" s="133">
         <f t="shared" ref="F53:F57" si="8">D53*8.09%</f>
-        <v>10283.451407999999</v>
+        <v>12442.9863</v>
       </c>
       <c r="G53" s="108">
-        <f t="shared" ref="G53:G70" si="9">D53</f>
-        <v>127113.12</v>
+        <f t="shared" ref="G53:G67" si="9">D53</f>
+        <v>153807</v>
       </c>
       <c r="H53" s="156">
-        <f t="shared" ref="H53:H70" si="10">E53+F53</f>
-        <v>127113.11999999998</v>
-      </c>
-      <c r="I53" s="171"/>
-      <c r="J53" s="171"/>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+        <f t="shared" ref="H53:H67" si="10">E53+F53</f>
+        <v>153806.99999999997</v>
+      </c>
+      <c r="I53" s="170"/>
+      <c r="J53" s="170"/>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="94" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="112">
-        <v>148200</v>
+        <v>0</v>
       </c>
       <c r="E54" s="145">
         <f t="shared" si="7"/>
-        <v>136210.62</v>
+        <v>0</v>
       </c>
       <c r="F54" s="133">
         <f t="shared" si="8"/>
-        <v>11989.38</v>
+        <v>0</v>
       </c>
       <c r="G54" s="108">
         <f t="shared" si="9"/>
-        <v>148200</v>
+        <v>0</v>
       </c>
       <c r="H54" s="156">
         <f t="shared" si="10"/>
-        <v>148200</v>
-      </c>
-      <c r="I54" s="171">
-        <f t="shared" ref="I54:I69" si="11">H54-D54</f>
-        <v>0</v>
-      </c>
-      <c r="J54" s="171">
-        <f t="shared" ref="J54:J70" si="12">G54-D54</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="I54" s="170">
+        <f t="shared" ref="I54:I64" si="11">H54-D54</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="170">
+        <f t="shared" ref="J54:J67" si="12">G54-D54</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="94" t="s">
         <v>9</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="112">
@@ -2884,24 +2857,24 @@
         <f>E55+F55</f>
         <v>129319.99999999999</v>
       </c>
-      <c r="I55" s="171">
+      <c r="I55" s="170">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J55" s="171">
+      <c r="J55" s="170">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="B56" s="7" t="s">
-        <v>170</v>
+      <c r="B56" s="98" t="s">
+        <v>164</v>
       </c>
       <c r="C56" s="7"/>
-      <c r="D56" s="183">
+      <c r="D56" s="112">
         <v>641235.69999999995</v>
       </c>
       <c r="E56" s="145">
@@ -2920,1220 +2893,1073 @@
         <f t="shared" si="10"/>
         <v>641235.69999999995</v>
       </c>
-      <c r="I56" s="171">
+      <c r="I56" s="170">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J56" s="171">
+      <c r="J56" s="170">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="128" t="s">
         <v>10</v>
       </c>
       <c r="B57" s="98" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C57" s="98"/>
-      <c r="D57" s="183">
-        <v>2276949.4300000002</v>
+      <c r="D57" s="112">
+        <f>2276949.43-1173289.52</f>
+        <v>1103659.9100000001</v>
       </c>
       <c r="E57" s="145">
         <f t="shared" si="7"/>
-        <v>2092744.2211130001</v>
+        <v>1014373.823281</v>
       </c>
       <c r="F57" s="133">
         <f t="shared" si="8"/>
-        <v>184205.20888700002</v>
+        <v>89286.086719000014</v>
       </c>
       <c r="G57" s="108">
         <f t="shared" si="9"/>
-        <v>2276949.4300000002</v>
+        <v>1103659.9100000001</v>
       </c>
       <c r="H57" s="156">
         <f t="shared" si="10"/>
-        <v>2276949.4300000002</v>
-      </c>
-      <c r="I57" s="171">
+        <v>1103659.9100000001</v>
+      </c>
+      <c r="I57" s="170">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J57" s="171">
+      <c r="J57" s="170">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A58" s="212" t="s">
-        <v>157</v>
-      </c>
-      <c r="B58" s="213"/>
-      <c r="C58" s="214"/>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A58" s="208" t="s">
+        <v>168</v>
+      </c>
+      <c r="B58" s="209"/>
+      <c r="C58" s="210"/>
       <c r="D58" s="112">
-        <v>67000</v>
+        <v>50000</v>
       </c>
       <c r="E58" s="145">
-        <f t="shared" ref="E58" si="13">D58</f>
-        <v>67000</v>
+        <f t="shared" ref="E58:E61" si="13">D58</f>
+        <v>50000</v>
       </c>
       <c r="F58" s="133"/>
       <c r="G58" s="108">
         <f t="shared" si="9"/>
-        <v>67000</v>
+        <v>50000</v>
       </c>
       <c r="H58" s="156">
         <f t="shared" si="10"/>
-        <v>67000</v>
-      </c>
-      <c r="I58" s="171">
+        <v>50000</v>
+      </c>
+      <c r="I58" s="170">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J58" s="171">
+      <c r="J58" s="170">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="217" t="s">
-        <v>155</v>
-      </c>
-      <c r="B59" s="218"/>
-      <c r="C59" s="219"/>
+    <row r="59" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="213" t="s">
+        <v>161</v>
+      </c>
+      <c r="B59" s="214"/>
+      <c r="C59" s="215"/>
       <c r="D59" s="112">
-        <v>35500</v>
+        <v>159500</v>
       </c>
       <c r="E59" s="145">
-        <f t="shared" ref="E59:E63" si="14">D59*91.91%</f>
-        <v>32628.049999999996</v>
+        <f t="shared" ref="E59:E60" si="14">D59*91.91%</f>
+        <v>146596.44999999998</v>
       </c>
       <c r="F59" s="133">
-        <f t="shared" ref="F59:F63" si="15">D59*8.09%</f>
-        <v>2871.95</v>
+        <f t="shared" ref="F59:F60" si="15">D59*8.09%</f>
+        <v>12903.55</v>
       </c>
       <c r="G59" s="108">
         <f t="shared" si="9"/>
-        <v>35500</v>
+        <v>159500</v>
       </c>
       <c r="H59" s="156">
         <f t="shared" si="10"/>
-        <v>35499.999999999993</v>
-      </c>
-      <c r="I59" s="171"/>
-      <c r="J59" s="171"/>
-    </row>
-    <row r="60" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="217" t="s">
-        <v>156</v>
-      </c>
-      <c r="B60" s="218"/>
-      <c r="C60" s="219"/>
+        <v>159499.99999999997</v>
+      </c>
+      <c r="I59" s="170"/>
+      <c r="J59" s="170"/>
+    </row>
+    <row r="60" spans="1:16" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="189" t="s">
+        <v>157</v>
+      </c>
+      <c r="B60" s="190"/>
+      <c r="C60" s="191"/>
       <c r="D60" s="112">
-        <v>159500</v>
+        <v>30000</v>
       </c>
       <c r="E60" s="145">
         <f t="shared" si="14"/>
-        <v>146596.44999999998</v>
+        <v>27572.999999999996</v>
       </c>
       <c r="F60" s="133">
         <f t="shared" si="15"/>
-        <v>12903.55</v>
+        <v>2427</v>
       </c>
       <c r="G60" s="108">
         <f t="shared" si="9"/>
-        <v>159500</v>
+        <v>30000</v>
       </c>
       <c r="H60" s="156">
         <f t="shared" si="10"/>
-        <v>159499.99999999997</v>
-      </c>
-      <c r="I60" s="171"/>
-      <c r="J60" s="171"/>
-    </row>
-    <row r="61" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="217" t="s">
-        <v>154</v>
-      </c>
-      <c r="B61" s="218"/>
-      <c r="C61" s="219"/>
+        <v>29999.999999999996</v>
+      </c>
+      <c r="I60" s="170"/>
+      <c r="J60" s="170"/>
+    </row>
+    <row r="61" spans="1:16" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="246" t="s">
+        <v>158</v>
+      </c>
+      <c r="B61" s="190"/>
+      <c r="C61" s="191"/>
       <c r="D61" s="112">
-        <v>170000</v>
+        <v>250000</v>
       </c>
       <c r="E61" s="145">
-        <f t="shared" si="14"/>
-        <v>156247</v>
-      </c>
-      <c r="F61" s="133">
-        <f t="shared" si="15"/>
-        <v>13753</v>
-      </c>
+        <f t="shared" si="13"/>
+        <v>250000</v>
+      </c>
+      <c r="F61" s="133"/>
       <c r="G61" s="108">
         <f t="shared" si="9"/>
-        <v>170000</v>
+        <v>250000</v>
       </c>
       <c r="H61" s="156">
         <f t="shared" si="10"/>
-        <v>170000</v>
-      </c>
-      <c r="I61" s="171"/>
-      <c r="J61" s="171"/>
-    </row>
-    <row r="62" spans="1:16" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="191" t="s">
-        <v>177</v>
-      </c>
-      <c r="B62" s="192"/>
-      <c r="C62" s="193"/>
-      <c r="D62" s="183">
-        <v>30000</v>
+        <v>250000</v>
+      </c>
+      <c r="I61" s="170"/>
+      <c r="J61" s="170"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A62" s="188" t="s">
+        <v>169</v>
+      </c>
+      <c r="B62" s="98"/>
+      <c r="C62" s="98"/>
+      <c r="D62" s="112">
+        <v>280000</v>
       </c>
       <c r="E62" s="145">
-        <f t="shared" si="14"/>
-        <v>27572.999999999996</v>
+        <f t="shared" ref="E62:E65" si="16">D62*91.91%</f>
+        <v>257347.99999999997</v>
       </c>
       <c r="F62" s="133">
-        <f t="shared" si="15"/>
-        <v>2427</v>
+        <f t="shared" ref="F62:F66" si="17">D62*8.09%</f>
+        <v>22652</v>
       </c>
       <c r="G62" s="108">
         <f t="shared" si="9"/>
-        <v>30000</v>
+        <v>280000</v>
       </c>
       <c r="H62" s="156">
         <f t="shared" si="10"/>
-        <v>29999.999999999996</v>
-      </c>
-      <c r="I62" s="171"/>
-      <c r="J62" s="171"/>
-    </row>
-    <row r="63" spans="1:16" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="247" t="s">
-        <v>179</v>
-      </c>
-      <c r="B63" s="192"/>
-      <c r="C63" s="193"/>
-      <c r="D63" s="183">
-        <v>250000</v>
+        <v>280000</v>
+      </c>
+      <c r="I62" s="170">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J62" s="170">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M62" s="181" t="s">
+        <v>137</v>
+      </c>
+      <c r="N62" s="7"/>
+      <c r="O62" s="7"/>
+      <c r="P62" s="182">
+        <v>358487.12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B63" s="98"/>
+      <c r="C63" s="98"/>
+      <c r="D63" s="112">
+        <v>84865.78</v>
       </c>
       <c r="E63" s="145">
-        <f t="shared" si="14"/>
-        <v>229774.99999999997</v>
-      </c>
-      <c r="F63" s="133">
-        <f t="shared" si="15"/>
-        <v>20225</v>
-      </c>
+        <f t="shared" ref="E63:E64" si="18">D63</f>
+        <v>84865.78</v>
+      </c>
+      <c r="F63" s="133"/>
       <c r="G63" s="108">
         <f t="shared" si="9"/>
-        <v>250000</v>
+        <v>84865.78</v>
       </c>
       <c r="H63" s="156">
         <f t="shared" si="10"/>
-        <v>249999.99999999997</v>
-      </c>
-      <c r="I63" s="171"/>
-      <c r="J63" s="171"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A64" s="190" t="s">
-        <v>181</v>
-      </c>
-      <c r="B64" s="98"/>
-      <c r="C64" s="98"/>
-      <c r="D64" s="183">
-        <v>159500</v>
+        <v>84865.78</v>
+      </c>
+      <c r="I63" s="170"/>
+      <c r="J63" s="170"/>
+    </row>
+    <row r="64" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B64" s="7"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="112">
+        <v>86478.23</v>
       </c>
       <c r="E64" s="145">
-        <f t="shared" ref="E64:E67" si="16">D64*91.91%</f>
-        <v>146596.44999999998</v>
-      </c>
-      <c r="F64" s="133">
-        <f t="shared" ref="F64:F70" si="17">D64*8.09%</f>
-        <v>12903.55</v>
-      </c>
+        <f t="shared" si="18"/>
+        <v>86478.23</v>
+      </c>
+      <c r="F64" s="133"/>
       <c r="G64" s="108">
         <f t="shared" si="9"/>
-        <v>159500</v>
+        <v>86478.23</v>
       </c>
       <c r="H64" s="156">
         <f t="shared" si="10"/>
-        <v>159499.99999999997</v>
-      </c>
-      <c r="I64" s="171">
+        <v>86478.23</v>
+      </c>
+      <c r="I64" s="170">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J64" s="171">
+      <c r="J64" s="170">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="M64" s="182" t="s">
-        <v>137</v>
-      </c>
-      <c r="N64" s="7"/>
-      <c r="O64" s="7"/>
-      <c r="P64" s="183">
-        <v>358487.12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A65" s="190" t="s">
-        <v>137</v>
-      </c>
-      <c r="B65" s="98" t="s">
-        <v>144</v>
-      </c>
-      <c r="C65" s="98"/>
+    </row>
+    <row r="65" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="120" t="s">
+        <v>171</v>
+      </c>
+      <c r="B65" s="113"/>
+      <c r="C65" s="7"/>
       <c r="D65" s="112">
-        <v>199992.75</v>
+        <v>31240.34</v>
       </c>
       <c r="E65" s="145">
-        <f>D65*91.91%</f>
-        <v>183813.33652499999</v>
+        <f t="shared" si="16"/>
+        <v>28712.996493999999</v>
       </c>
       <c r="F65" s="133">
         <f t="shared" si="17"/>
-        <v>16179.413474999999</v>
+        <v>2527.3435060000002</v>
       </c>
       <c r="G65" s="108">
         <f t="shared" si="9"/>
-        <v>199992.75</v>
+        <v>31240.34</v>
       </c>
       <c r="H65" s="156">
         <f t="shared" si="10"/>
-        <v>199992.75</v>
-      </c>
-      <c r="I65" s="171">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J65" s="171">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="B66" s="98"/>
-      <c r="C66" s="98"/>
-      <c r="D66" s="183">
-        <v>84865.78</v>
+        <v>31240.34</v>
+      </c>
+      <c r="I65" s="170"/>
+      <c r="J65" s="170"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="120" t="s">
+        <v>170</v>
+      </c>
+      <c r="B66" s="113"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="112">
+        <v>40000</v>
       </c>
       <c r="E66" s="145">
         <f>D66*91.91%</f>
-        <v>78000.138397999996</v>
+        <v>36764</v>
       </c>
       <c r="F66" s="133">
         <f t="shared" si="17"/>
-        <v>6865.6416019999997</v>
+        <v>3236</v>
       </c>
       <c r="G66" s="108">
         <f t="shared" si="9"/>
-        <v>84865.78</v>
+        <v>40000</v>
       </c>
       <c r="H66" s="156">
         <f t="shared" si="10"/>
-        <v>84865.78</v>
-      </c>
-      <c r="I66" s="171"/>
-      <c r="J66" s="171"/>
-    </row>
-    <row r="67" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="B67" s="7"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="183">
-        <v>86478.23</v>
+        <v>40000</v>
+      </c>
+      <c r="I66" s="170"/>
+      <c r="J66" s="170"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="247" t="s">
+        <v>159</v>
+      </c>
+      <c r="B67" s="151"/>
+      <c r="C67" s="151"/>
+      <c r="D67" s="245">
+        <v>95800</v>
       </c>
       <c r="E67" s="145">
-        <f t="shared" si="16"/>
-        <v>79482.141192999989</v>
-      </c>
-      <c r="F67" s="133">
-        <f t="shared" si="17"/>
-        <v>6996.0888070000001</v>
-      </c>
+        <f t="shared" ref="E67" si="19">D67</f>
+        <v>95800</v>
+      </c>
+      <c r="F67" s="133"/>
       <c r="G67" s="108">
         <f t="shared" si="9"/>
-        <v>86478.23</v>
+        <v>95800</v>
       </c>
       <c r="H67" s="156">
         <f t="shared" si="10"/>
-        <v>86478.229999999981</v>
-      </c>
-      <c r="I67" s="171">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J67" s="171">
+        <v>95800</v>
+      </c>
+      <c r="I67" t="str">
+        <f>IF(G67=H67, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J67" s="170">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="120" t="s">
-        <v>175</v>
-      </c>
-      <c r="B68" s="113"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="112">
-        <v>360000</v>
-      </c>
-      <c r="E68" s="145">
-        <f>D68*91.91%</f>
-        <v>330875.99999999994</v>
-      </c>
-      <c r="F68" s="133">
-        <f t="shared" si="17"/>
-        <v>29124</v>
-      </c>
-      <c r="G68" s="108"/>
-      <c r="H68" s="156"/>
-      <c r="I68" s="171"/>
-      <c r="J68" s="171"/>
-    </row>
-    <row r="69" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="246" t="s">
-        <v>178</v>
-      </c>
-      <c r="B69" s="113"/>
-      <c r="C69" s="157"/>
-      <c r="D69" s="183">
-        <v>40000</v>
-      </c>
-      <c r="E69" s="145">
-        <f t="shared" ref="E69:E70" si="18">D69*91.91%</f>
-        <v>36764</v>
-      </c>
-      <c r="F69" s="133">
-        <f t="shared" si="17"/>
-        <v>3236</v>
-      </c>
-      <c r="G69" s="108">
-        <f t="shared" si="9"/>
-        <v>40000</v>
-      </c>
-      <c r="H69" s="156">
-        <f t="shared" si="10"/>
-        <v>40000</v>
-      </c>
-      <c r="I69" s="171">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J69" s="171">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A70" s="194" t="s">
-        <v>180</v>
-      </c>
-      <c r="B70" s="151"/>
-      <c r="C70" s="151"/>
-      <c r="D70" s="248">
-        <v>95800</v>
-      </c>
-      <c r="E70" s="145">
-        <f t="shared" si="18"/>
-        <v>88049.78</v>
-      </c>
-      <c r="F70" s="133">
-        <f t="shared" si="17"/>
-        <v>7750.22</v>
-      </c>
-      <c r="G70" s="108">
-        <f t="shared" si="9"/>
-        <v>95800</v>
-      </c>
-      <c r="H70" s="156">
-        <f t="shared" si="10"/>
-        <v>95800</v>
-      </c>
-      <c r="I70" t="str">
-        <f>IF(G70=H70, "", "Error")</f>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="95" t="s">
+        <v>12</v>
+      </c>
+      <c r="B68" s="96"/>
+      <c r="C68" s="96"/>
+      <c r="D68" s="107">
+        <f>SUM(D51:D67)</f>
+        <v>3507906.96</v>
+      </c>
+      <c r="E68" s="107">
+        <f>SUM(E51:E67)</f>
+        <v>3300094.0373449996</v>
+      </c>
+      <c r="F68" s="107">
+        <f>SUM(F51:F67)</f>
+        <v>207812.922655</v>
+      </c>
+      <c r="G68" s="108">
+        <f>E68+F68</f>
+        <v>3507906.9599999995</v>
+      </c>
+      <c r="H68" s="146" t="str">
+        <f>IF(D68=G68, "", "Error")</f>
         <v/>
       </c>
-      <c r="J70" s="171">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A71" s="95" t="s">
-        <v>12</v>
-      </c>
-      <c r="B71" s="96"/>
-      <c r="C71" s="96"/>
-      <c r="D71" s="107">
-        <f>SUM(D51:D70)</f>
-        <v>5593455.0100000007</v>
-      </c>
-      <c r="E71" s="107">
-        <f>SUM(E51:E70)</f>
-        <v>5189403.5996909998</v>
-      </c>
-      <c r="F71" s="107">
-        <f>SUM(F51:F70)</f>
-        <v>404051.410309</v>
-      </c>
-      <c r="G71" s="108">
-        <f>E71+F71</f>
-        <v>5593455.0099999998</v>
-      </c>
-      <c r="H71" s="146" t="str">
-        <f>IF(D71=G71, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="I71" s="171">
-        <f>D71-G71</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="7"/>
-      <c r="B72" s="7"/>
+      <c r="I68" s="170">
+        <f>D68-G68</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="7"/>
+      <c r="B69" s="7"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="175"/>
+      <c r="E69" s="114"/>
+      <c r="F69" s="7"/>
+      <c r="H69" s="146"/>
+    </row>
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="7"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="175"/>
+      <c r="E70" s="113"/>
+      <c r="F70" s="7"/>
+      <c r="H70" s="146"/>
+    </row>
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="7"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="7"/>
+      <c r="D71" s="175"/>
+      <c r="E71" s="113"/>
+      <c r="F71" s="7"/>
+      <c r="H71" s="146"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="94" t="s">
+        <v>141</v>
+      </c>
+      <c r="B72" s="98"/>
       <c r="C72" s="7"/>
-      <c r="D72" s="176"/>
-      <c r="E72" s="114"/>
-      <c r="F72" s="7"/>
+      <c r="D72" s="112">
+        <v>108000</v>
+      </c>
+      <c r="E72" s="145">
+        <f>D72*91.91%</f>
+        <v>99262.799999999988</v>
+      </c>
+      <c r="F72" s="133">
+        <f>D72*8.09%</f>
+        <v>8737.2000000000007</v>
+      </c>
+      <c r="G72" s="155"/>
       <c r="H72" s="146"/>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
-      <c r="D73" s="176"/>
-      <c r="E73" s="113"/>
+      <c r="D73" s="112"/>
+      <c r="E73" s="158">
+        <f>D73</f>
+        <v>0</v>
+      </c>
       <c r="F73" s="7"/>
       <c r="H73" s="146"/>
-    </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="7"/>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="176"/>
-      <c r="E74" s="113"/>
-      <c r="F74" s="7"/>
-      <c r="H74" s="146"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" s="94" t="s">
-        <v>141</v>
-      </c>
-      <c r="B75" s="98"/>
+      <c r="I73" s="108"/>
+    </row>
+    <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="95" t="s">
+        <v>16</v>
+      </c>
+      <c r="B74" s="95"/>
+      <c r="C74" s="95"/>
+      <c r="D74" s="107">
+        <f>SUM(D72:D73)</f>
+        <v>108000</v>
+      </c>
+      <c r="E74" s="107">
+        <f>SUM(E72:E73)</f>
+        <v>99262.799999999988</v>
+      </c>
+      <c r="F74" s="107">
+        <f>SUM(F72:F73)</f>
+        <v>8737.2000000000007</v>
+      </c>
+      <c r="G74" s="108">
+        <f>E74+F74</f>
+        <v>107999.99999999999</v>
+      </c>
+      <c r="H74" s="146" t="str">
+        <f>IF(D74=G74, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J74" s="108"/>
+    </row>
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="7"/>
+      <c r="B75" s="7"/>
       <c r="C75" s="7"/>
-      <c r="D75" s="183">
-        <v>108000</v>
-      </c>
-      <c r="E75" s="145">
-        <f>D75*91.91%</f>
-        <v>99262.799999999988</v>
-      </c>
-      <c r="F75" s="133">
-        <f>D75*8.09%</f>
-        <v>8737.2000000000007</v>
-      </c>
-      <c r="G75" s="155"/>
+      <c r="D75" s="175"/>
+      <c r="E75" s="114"/>
+      <c r="F75" s="7"/>
       <c r="H75" s="146"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
-      <c r="D76" s="112"/>
-      <c r="E76" s="159">
-        <f>D76</f>
-        <v>0</v>
-      </c>
+      <c r="D76" s="175"/>
+      <c r="E76" s="113"/>
       <c r="F76" s="7"/>
       <c r="H76" s="146"/>
-      <c r="I76" s="108"/>
-    </row>
-    <row r="77" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="95" t="s">
-        <v>16</v>
-      </c>
-      <c r="B77" s="95"/>
-      <c r="C77" s="95"/>
-      <c r="D77" s="107">
-        <f>SUM(D75:D76)</f>
-        <v>108000</v>
-      </c>
-      <c r="E77" s="107">
-        <f>SUM(E75:E76)</f>
-        <v>99262.799999999988</v>
-      </c>
-      <c r="F77" s="107">
-        <f>SUM(F75:F76)</f>
-        <v>8737.2000000000007</v>
-      </c>
-      <c r="G77" s="108">
-        <f>E77+F77</f>
-        <v>107999.99999999999</v>
-      </c>
-      <c r="H77" s="146" t="str">
-        <f>IF(D77=G77, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="J77" s="108"/>
-    </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="7"/>
-      <c r="B78" s="7"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="94" t="s">
+        <v>13</v>
+      </c>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="175"/>
+      <c r="E77" s="113"/>
+      <c r="F77" s="7"/>
+      <c r="H77" s="146"/>
+    </row>
+    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="94" t="s">
+        <v>14</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>116</v>
+      </c>
       <c r="C78" s="7"/>
-      <c r="D78" s="176"/>
-      <c r="E78" s="114"/>
-      <c r="F78" s="7"/>
+      <c r="D78" s="112">
+        <v>246000</v>
+      </c>
+      <c r="E78" s="145">
+        <f>D78*91.91%</f>
+        <v>226098.59999999998</v>
+      </c>
+      <c r="F78" s="133">
+        <f>D78*8.09%</f>
+        <v>19901.400000000001</v>
+      </c>
+      <c r="G78" t="s">
+        <v>139</v>
+      </c>
       <c r="H78" s="146"/>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="7"/>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="94" t="s">
+        <v>107</v>
+      </c>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
-      <c r="D79" s="176"/>
-      <c r="E79" s="113"/>
-      <c r="F79" s="7"/>
+      <c r="D79" s="112">
+        <v>30000</v>
+      </c>
+      <c r="E79" s="145">
+        <f>D79*91.91%</f>
+        <v>27572.999999999996</v>
+      </c>
+      <c r="F79" s="133">
+        <f>D79*8.09%</f>
+        <v>2427</v>
+      </c>
       <c r="H79" s="146"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" s="94" t="s">
-        <v>13</v>
-      </c>
+      <c r="J79" s="112"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
-      <c r="D80" s="176"/>
-      <c r="E80" s="113"/>
+      <c r="D80" s="175"/>
+      <c r="E80" s="115"/>
       <c r="F80" s="7"/>
       <c r="H80" s="146"/>
-    </row>
-    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="94" t="s">
-        <v>14</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C81" s="7"/>
-      <c r="D81" s="183">
-        <v>246000</v>
-      </c>
-      <c r="E81" s="145">
-        <f>D81*91.91%</f>
-        <v>226098.59999999998</v>
-      </c>
-      <c r="F81" s="133">
-        <f>D81*8.09%</f>
-        <v>19901.400000000001</v>
-      </c>
-      <c r="G81" t="s">
-        <v>139</v>
-      </c>
-      <c r="H81" s="146"/>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J80" s="108"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="95" t="s">
+        <v>100</v>
+      </c>
+      <c r="B81" s="95"/>
+      <c r="C81" s="95"/>
+      <c r="D81" s="107">
+        <f>SUM(D78:D80)</f>
+        <v>276000</v>
+      </c>
+      <c r="E81" s="107">
+        <f>SUM(E78:E80)</f>
+        <v>253671.59999999998</v>
+      </c>
+      <c r="F81" s="107">
+        <f>SUM(F78:F80)</f>
+        <v>22328.400000000001</v>
+      </c>
+      <c r="G81" s="108">
+        <f>E81+F81</f>
+        <v>276000</v>
+      </c>
+      <c r="H81" s="146" t="str">
+        <f>IF(D81=G81, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J81" s="108"/>
+    </row>
+    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="94" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
-      <c r="D82" s="112">
-        <v>30000</v>
-      </c>
-      <c r="E82" s="145">
-        <f>D82*91.91%</f>
-        <v>27572.999999999996</v>
-      </c>
-      <c r="F82" s="133">
-        <f>D82*8.09%</f>
-        <v>2427</v>
-      </c>
+      <c r="D82" s="112"/>
+      <c r="E82" s="116"/>
+      <c r="F82" s="7"/>
       <c r="H82" s="146"/>
-      <c r="J82" s="112"/>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A83" s="7"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="94" t="s">
+        <v>101</v>
+      </c>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
-      <c r="D83" s="176"/>
-      <c r="E83" s="115"/>
-      <c r="F83" s="7"/>
+      <c r="D83" s="112">
+        <v>230178.74</v>
+      </c>
+      <c r="E83" s="145">
+        <f>D83*91.91%</f>
+        <v>211557.27993399996</v>
+      </c>
+      <c r="F83" s="133">
+        <f>D83*8.09%</f>
+        <v>18621.460066</v>
+      </c>
       <c r="H83" s="146"/>
-      <c r="J83" s="108"/>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A84" s="95" t="s">
-        <v>100</v>
-      </c>
-      <c r="B84" s="95"/>
-      <c r="C84" s="95"/>
-      <c r="D84" s="107">
-        <f>SUM(D81:D83)</f>
-        <v>276000</v>
-      </c>
-      <c r="E84" s="107">
-        <f>SUM(E81:E83)</f>
-        <v>253671.59999999998</v>
-      </c>
-      <c r="F84" s="107">
-        <f>SUM(F81:F83)</f>
-        <v>22328.400000000001</v>
-      </c>
-      <c r="G84" s="108">
-        <f>E84+F84</f>
-        <v>276000</v>
-      </c>
-      <c r="H84" s="146" t="str">
-        <f>IF(D84=G84, "", "Error")</f>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="B84" s="7"/>
+      <c r="C84" s="121"/>
+      <c r="D84" s="112">
+        <v>44400</v>
+      </c>
+      <c r="E84" s="145">
+        <f>D84*91.91%</f>
+        <v>40808.039999999994</v>
+      </c>
+      <c r="F84" s="133">
+        <f>D84*8.09%</f>
+        <v>3591.96</v>
+      </c>
+      <c r="H84" s="146"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" s="95"/>
+      <c r="C85" s="95"/>
+      <c r="D85" s="153">
+        <f>SUM(D83:D84)</f>
+        <v>274578.74</v>
+      </c>
+      <c r="E85" s="143">
+        <f t="shared" ref="E85:F85" si="20">SUM(E83:E84)</f>
+        <v>252365.31993399997</v>
+      </c>
+      <c r="F85" s="143">
+        <f t="shared" si="20"/>
+        <v>22213.420065999999</v>
+      </c>
+      <c r="G85" s="108">
+        <f>E85+F85</f>
+        <v>274578.74</v>
+      </c>
+      <c r="H85" s="146" t="str">
+        <f>IF(D85=G85, "", "Error")</f>
         <v/>
       </c>
-      <c r="J84" s="108"/>
-    </row>
-    <row r="85" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="94" t="s">
-        <v>100</v>
-      </c>
-      <c r="B85" s="7"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="112"/>
-      <c r="E85" s="116"/>
-      <c r="F85" s="7"/>
-      <c r="H85" s="146"/>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A86" s="94" t="s">
-        <v>101</v>
-      </c>
+    </row>
+    <row r="86" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
-      <c r="D86" s="112">
-        <v>114083.66</v>
-      </c>
-      <c r="E86" s="145">
-        <f>D86*91.91%</f>
-        <v>104854.291906</v>
-      </c>
-      <c r="F86" s="133">
-        <f>D86*8.09%</f>
-        <v>9229.3680939999995</v>
-      </c>
+      <c r="D86" s="176"/>
+      <c r="E86" s="12"/>
+      <c r="F86" s="7"/>
       <c r="H86" s="146"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A87" s="94" t="s">
-        <v>102</v>
-      </c>
-      <c r="B87" s="7"/>
-      <c r="C87" s="121"/>
-      <c r="D87" s="112">
-        <v>44400</v>
-      </c>
-      <c r="E87" s="145">
+    <row r="87" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="99" t="s">
+        <v>133</v>
+      </c>
+      <c r="B87" s="99"/>
+      <c r="C87" s="99"/>
+      <c r="D87" s="177">
+        <f>7000000-5970688.01</f>
+        <v>1029311.9900000002</v>
+      </c>
+      <c r="E87" s="117">
         <f>D87*91.91%</f>
-        <v>40808.039999999994</v>
-      </c>
-      <c r="F87" s="133">
+        <v>946040.65000900009</v>
+      </c>
+      <c r="F87" s="135">
         <f>D87*8.09%</f>
-        <v>3591.96</v>
-      </c>
-      <c r="H87" s="146"/>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A88" s="95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" s="95"/>
-      <c r="C88" s="95"/>
-      <c r="D88" s="153">
-        <f>SUM(D86:D87)</f>
-        <v>158483.66</v>
-      </c>
-      <c r="E88" s="143">
-        <f t="shared" ref="E88:F88" si="19">SUM(E86:E87)</f>
-        <v>145662.33190599998</v>
-      </c>
-      <c r="F88" s="143">
-        <f t="shared" si="19"/>
-        <v>12821.328094</v>
-      </c>
-      <c r="G88" s="108">
-        <f>E88+F88</f>
-        <v>158483.65999999997</v>
-      </c>
-      <c r="H88" s="146" t="str">
-        <f>IF(D88=G88, "", "Error")</f>
+        <v>83271.339991000015</v>
+      </c>
+      <c r="G87" s="108">
+        <f>E87+F87</f>
+        <v>1029311.9900000001</v>
+      </c>
+      <c r="H87" s="146" t="str">
+        <f>IF(D87=G87, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="7"/>
-      <c r="B89" s="7"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="177"/>
-      <c r="E89" s="12"/>
-      <c r="F89" s="7"/>
-      <c r="H89" s="146"/>
-    </row>
-    <row r="90" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="99" t="s">
-        <v>133</v>
-      </c>
-      <c r="B90" s="99"/>
-      <c r="C90" s="99"/>
-      <c r="D90" s="178">
-        <f>9512420-5682222.96</f>
-        <v>3830197.04</v>
-      </c>
-      <c r="E90" s="117">
-        <f>D90*91.91%</f>
-        <v>3520334.0994639997</v>
-      </c>
-      <c r="F90" s="135">
-        <f>D90*8.09%</f>
-        <v>309862.94053600001</v>
-      </c>
-      <c r="G90" s="108">
-        <f>E90+F90</f>
-        <v>3830197.0399999996</v>
-      </c>
-      <c r="H90" s="146" t="str">
-        <f>IF(D90=G90, "", "Error")</f>
+    <row r="88" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="1"/>
+      <c r="D88" s="174"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="10"/>
+      <c r="G88" s="152"/>
+      <c r="H88" s="146"/>
+    </row>
+    <row r="89" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B89" s="60"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="178">
+        <f>SUM(D87+D85+D81+D74+D68+D49+D32+D27+D44)</f>
+        <v>7000000</v>
+      </c>
+      <c r="E89" s="144">
+        <f>SUM(E87+E85+E81+E74+E68+E49+E32+E27+E44)</f>
+        <v>6509676.7504089996</v>
+      </c>
+      <c r="F89" s="144">
+        <f>SUM(F87+F85+F81+F74+F68+F49+F32+F27+F44)</f>
+        <v>490323.24959100003</v>
+      </c>
+      <c r="G89" s="108">
+        <f>E89+F89</f>
+        <v>7000000</v>
+      </c>
+      <c r="H89" s="146" t="str">
+        <f>IF(D89=G89, "", "Error")</f>
         <v/>
       </c>
-    </row>
-    <row r="91" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="1"/>
-      <c r="D91" s="175"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="10"/>
-      <c r="G91" s="152"/>
-      <c r="H91" s="146"/>
-    </row>
-    <row r="92" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B92" s="60"/>
-      <c r="C92" s="5"/>
-      <c r="D92" s="179">
-        <f>SUM(D90+D88+D84+D77+D71+D49+D32+D27+D44)</f>
-        <v>11708794.020000001</v>
-      </c>
-      <c r="E92" s="144">
-        <f>SUM(E90+E88+E84+E77+E71+E49+E32+E27+E44)</f>
-        <v>10810011.683782</v>
-      </c>
-      <c r="F92" s="144">
-        <f>SUM(F90+F88+F84+F77+F71+F49+F32+F27+F44)</f>
-        <v>898782.33621800004</v>
-      </c>
-      <c r="G92" s="108">
-        <f>E92+F92</f>
-        <v>11708794.02</v>
-      </c>
-      <c r="H92" s="146" t="str">
-        <f>IF(D92=G92, "", "Error")</f>
+      <c r="I89" s="170">
+        <f>D89-G89</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D90" s="174"/>
+      <c r="E90" s="108"/>
+    </row>
+    <row r="91" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="184" t="s">
+        <v>152</v>
+      </c>
+      <c r="B91" s="140"/>
+      <c r="C91" s="140"/>
+      <c r="E91" s="108"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" s="1"/>
+      <c r="C92" s="138"/>
+      <c r="E92" s="108"/>
+    </row>
+    <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="1"/>
+      <c r="C93" s="138"/>
+      <c r="E93" s="108"/>
+    </row>
+    <row r="94" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="141" t="s">
+        <v>29</v>
+      </c>
+      <c r="B94" s="142"/>
+      <c r="C94" s="139">
+        <f>SUM(C92:C93)</f>
+        <v>0</v>
+      </c>
+      <c r="E94" s="108"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E95" s="108"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E96" s="136"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="211" t="s">
+        <v>113</v>
+      </c>
+      <c r="B97" s="212"/>
+      <c r="C97" s="212"/>
+      <c r="D97" s="212"/>
+      <c r="E97" s="164" t="s">
+        <v>21</v>
+      </c>
+      <c r="F97" s="165" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="213" t="s">
+        <v>160</v>
+      </c>
+      <c r="B98" s="214"/>
+      <c r="C98" s="215"/>
+      <c r="D98" s="112">
+        <v>317050.40000000002</v>
+      </c>
+      <c r="E98" s="145">
+        <f t="shared" ref="E98:E99" si="21">D98*91.91%</f>
+        <v>291401.02263999998</v>
+      </c>
+      <c r="F98" s="133">
+        <f t="shared" ref="F98:F99" si="22">D98*8.09%</f>
+        <v>25649.377360000002</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="241" t="s">
+        <v>172</v>
+      </c>
+      <c r="B99" s="242"/>
+      <c r="C99" s="243"/>
+      <c r="D99" s="112">
+        <v>110000</v>
+      </c>
+      <c r="E99" s="145">
+        <f t="shared" si="21"/>
+        <v>101100.99999999999</v>
+      </c>
+      <c r="F99" s="133">
+        <f t="shared" si="22"/>
+        <v>8899</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="205" t="s">
+        <v>29</v>
+      </c>
+      <c r="B100" s="206"/>
+      <c r="C100" s="207"/>
+      <c r="D100" s="163">
+        <f>SUM(D98:D99)</f>
+        <v>427050.4</v>
+      </c>
+      <c r="E100" s="163">
+        <f>SUM(E98:E99)</f>
+        <v>392502.02263999998</v>
+      </c>
+      <c r="F100" s="163">
+        <f>SUM(F98:F99)</f>
+        <v>34548.377359999999</v>
+      </c>
+      <c r="H100" s="108">
+        <f>E100+F100</f>
+        <v>427050.39999999997</v>
+      </c>
+      <c r="I100" s="146" t="str">
+        <f>IF(D100=H100, "", "Error")</f>
         <v/>
       </c>
-      <c r="I92" s="171">
-        <f>D92-G92</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D93" s="175"/>
-      <c r="E93" s="108"/>
-    </row>
-    <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="186" t="s">
-        <v>169</v>
-      </c>
-      <c r="B94" s="140"/>
-      <c r="C94" s="140"/>
-      <c r="E94" s="108"/>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A95" s="1"/>
-      <c r="C95" s="138"/>
-      <c r="E95" s="108"/>
-    </row>
-    <row r="96" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="1"/>
-      <c r="C96" s="138"/>
-      <c r="E96" s="108"/>
-    </row>
-    <row r="97" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="141" t="s">
+    </row>
+    <row r="102" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E102" s="108"/>
+    </row>
+    <row r="103" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="102" t="s">
+        <v>104</v>
+      </c>
+      <c r="B103" s="103">
+        <f>D89</f>
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="104" t="s">
+        <v>106</v>
+      </c>
+      <c r="B104" s="105">
+        <f>D89-D87</f>
+        <v>5970688.0099999998</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D105" s="195"/>
+      <c r="E105" s="195"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="74" t="s">
+        <v>90</v>
+      </c>
+      <c r="B106" s="75"/>
+      <c r="C106" s="76"/>
+      <c r="D106" s="195"/>
+      <c r="E106" s="195"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="B107" s="11">
+        <v>-3514251.2083843551</v>
+      </c>
+      <c r="C107" s="78"/>
+      <c r="D107" s="195"/>
+      <c r="E107" s="195"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="79" t="s">
+        <v>92</v>
+      </c>
+      <c r="B108" s="92">
+        <f>PRORRATEO!G52</f>
+        <v>13569486.916373972</v>
+      </c>
+      <c r="C108" s="78" t="s">
+        <v>93</v>
+      </c>
+      <c r="D108" s="195"/>
+      <c r="E108" s="195"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="79" t="s">
+        <v>115</v>
+      </c>
+      <c r="B109" s="167">
+        <f>-B104</f>
+        <v>-5970688.0099999998</v>
+      </c>
+      <c r="C109" s="76"/>
+      <c r="D109" s="195"/>
+      <c r="E109" s="195"/>
+      <c r="G109" s="112"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="79" t="s">
+        <v>114</v>
+      </c>
+      <c r="B110" s="167">
+        <f>-D100</f>
+        <v>-427050.4</v>
+      </c>
+      <c r="C110" s="76"/>
+      <c r="D110" s="195"/>
+      <c r="E110" s="195"/>
+      <c r="G110" s="124"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="79" t="s">
+        <v>105</v>
+      </c>
+      <c r="B111" s="167">
+        <f>-B118</f>
+        <v>-40000</v>
+      </c>
+      <c r="C111" s="80"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="79" t="s">
+        <v>120</v>
+      </c>
+      <c r="B112" s="93">
+        <f>-C94</f>
+        <v>0</v>
+      </c>
+      <c r="C112" s="80"/>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A113" s="79"/>
+      <c r="B113" s="75"/>
+      <c r="C113" s="150"/>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A114" s="77" t="s">
+        <v>94</v>
+      </c>
+      <c r="B114" s="81">
+        <f>SUM(B107:B113)</f>
+        <v>3617497.2979896166</v>
+      </c>
+      <c r="C114" s="150"/>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A115" s="80"/>
+      <c r="C115" s="76"/>
+      <c r="D115" s="83"/>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C116" s="76"/>
+      <c r="D116" s="108"/>
+      <c r="E116" s="170"/>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A117" s="74" t="s">
+        <v>95</v>
+      </c>
+      <c r="B117" s="11">
+        <v>-312694.54000000004</v>
+      </c>
+      <c r="C117" s="82"/>
+      <c r="D117" s="170"/>
+      <c r="E117" s="170"/>
+      <c r="F117" s="170"/>
+    </row>
+    <row r="118" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="77" t="s">
+        <v>156</v>
+      </c>
+      <c r="B118" s="93">
+        <v>40000</v>
+      </c>
+      <c r="C118" s="82"/>
+      <c r="D118" s="170"/>
+      <c r="E118" s="180"/>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A119" s="77"/>
+      <c r="B119" s="167"/>
+      <c r="C119" s="82"/>
+      <c r="E119" s="108"/>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A120" s="77"/>
+      <c r="B120" s="167"/>
+      <c r="C120" s="82"/>
+      <c r="E120" s="108"/>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A121" s="100" t="s">
         <v>29</v>
       </c>
-      <c r="B97" s="142"/>
-      <c r="C97" s="139">
-        <f>SUM(C95:C96)</f>
-        <v>0</v>
-      </c>
-      <c r="E97" s="108"/>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E98" s="108"/>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E99" s="136"/>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A100" s="215" t="s">
-        <v>113</v>
-      </c>
-      <c r="B100" s="216"/>
-      <c r="C100" s="216"/>
-      <c r="D100" s="216"/>
-      <c r="E100" s="165" t="s">
-        <v>21</v>
-      </c>
-      <c r="F100" s="166" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="212" t="s">
-        <v>167</v>
-      </c>
-      <c r="B101" s="213"/>
-      <c r="C101" s="214"/>
-      <c r="D101" s="112">
-        <v>1400000</v>
-      </c>
-      <c r="E101" s="145">
-        <f t="shared" ref="E101:E102" si="20">D101*91.91%</f>
-        <v>1286740</v>
-      </c>
-      <c r="F101" s="133">
-        <f t="shared" ref="F101:F103" si="21">D101*8.09%</f>
-        <v>113260</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="212" t="s">
-        <v>168</v>
-      </c>
-      <c r="B102" s="213"/>
-      <c r="C102" s="214"/>
-      <c r="D102" s="112">
-        <v>1000000</v>
-      </c>
-      <c r="E102" s="145">
-        <f t="shared" si="20"/>
-        <v>919099.99999999988</v>
-      </c>
-      <c r="F102" s="133">
-        <f t="shared" si="21"/>
-        <v>80900</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="185" t="s">
-        <v>163</v>
-      </c>
-      <c r="B103" s="113"/>
-      <c r="C103" s="195" t="s">
-        <v>165</v>
-      </c>
-      <c r="D103" s="112">
-        <v>260000</v>
-      </c>
-      <c r="E103" s="145">
-        <f t="shared" ref="E103" si="22">D103*91.91%</f>
-        <v>238965.99999999997</v>
-      </c>
-      <c r="F103" s="133">
-        <f t="shared" si="21"/>
-        <v>21034</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="185" t="s">
-        <v>164</v>
-      </c>
-      <c r="B104" s="113"/>
-      <c r="C104" s="195" t="s">
-        <v>165</v>
-      </c>
-      <c r="D104" s="112">
-        <v>256310.6</v>
-      </c>
-      <c r="E104" s="145">
-        <f>D104*91.91%</f>
-        <v>235575.07246</v>
-      </c>
-      <c r="F104" s="133">
-        <f>D104*8.09%</f>
-        <v>20735.527539999999</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A105" s="209" t="s">
-        <v>29</v>
-      </c>
-      <c r="B105" s="210"/>
-      <c r="C105" s="211"/>
-      <c r="D105" s="164">
-        <f>SUM(D101:D104)</f>
-        <v>2916310.6</v>
-      </c>
-      <c r="E105" s="164">
-        <f>SUM(E101:E104)</f>
-        <v>2680381.0724599999</v>
-      </c>
-      <c r="F105" s="164">
-        <f>SUM(F101:F104)</f>
-        <v>235929.52754000001</v>
-      </c>
-      <c r="H105" s="108">
-        <f>E105+F105</f>
-        <v>2916310.6</v>
-      </c>
-      <c r="I105" s="146" t="str">
-        <f>IF(D105=H105, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E107" s="108"/>
-    </row>
-    <row r="108" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="102" t="s">
-        <v>104</v>
-      </c>
-      <c r="B108" s="103">
-        <f>D92</f>
-        <v>11708794.020000001</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="104" t="s">
-        <v>106</v>
-      </c>
-      <c r="B109" s="105">
-        <f>D92-D90</f>
-        <v>7878596.9800000014</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D110" s="199"/>
-      <c r="E110" s="199"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A111" s="74" t="s">
-        <v>90</v>
-      </c>
-      <c r="B111" s="75"/>
-      <c r="C111" s="76"/>
-      <c r="D111" s="199"/>
-      <c r="E111" s="199"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A112" s="77" t="s">
-        <v>91</v>
-      </c>
-      <c r="B112" s="11">
-        <v>-3599025.7822533529</v>
-      </c>
-      <c r="C112" s="78"/>
-      <c r="D112" s="199"/>
-      <c r="E112" s="199"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A113" s="79" t="s">
-        <v>92</v>
-      </c>
-      <c r="B113" s="92">
-        <f>PRORRATEO!G52</f>
-        <v>8723308.1338689979</v>
-      </c>
-      <c r="C113" s="78" t="s">
-        <v>93</v>
-      </c>
-      <c r="D113" s="199"/>
-      <c r="E113" s="199"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A114" s="79" t="s">
-        <v>115</v>
-      </c>
-      <c r="B114" s="168">
-        <f>-B109</f>
-        <v>-7878596.9800000014</v>
-      </c>
-      <c r="C114" s="76"/>
-      <c r="D114" s="199"/>
-      <c r="E114" s="199"/>
-      <c r="G114" s="112"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A115" s="79" t="s">
-        <v>114</v>
-      </c>
-      <c r="B115" s="168">
-        <f>-D105</f>
-        <v>-2916310.6</v>
-      </c>
-      <c r="C115" s="76"/>
-      <c r="D115" s="199"/>
-      <c r="E115" s="199"/>
-      <c r="G115" s="124"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A116" s="79" t="s">
-        <v>105</v>
-      </c>
-      <c r="B116" s="168">
-        <f>-B123</f>
-        <v>-40000</v>
-      </c>
-      <c r="C116" s="80"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A117" s="79" t="s">
-        <v>120</v>
-      </c>
-      <c r="B117" s="93">
-        <f>-C97</f>
-        <v>0</v>
-      </c>
-      <c r="C117" s="80"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A118" s="79"/>
-      <c r="B118" s="75"/>
-      <c r="C118" s="80"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" s="77" t="s">
-        <v>94</v>
-      </c>
-      <c r="B119" s="81">
-        <f>SUM(B112:B118)</f>
-        <v>-5710625.2283843569</v>
-      </c>
-      <c r="C119" s="150"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" s="80"/>
-      <c r="C120" s="76"/>
-      <c r="D120" s="83"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C121" s="76"/>
-      <c r="D121" s="108"/>
-      <c r="E121" s="171"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" s="74" t="s">
-        <v>95</v>
-      </c>
-      <c r="B122" s="11">
-        <v>-352694.54000000004</v>
-      </c>
-      <c r="C122" s="82"/>
-      <c r="D122" s="171"/>
-      <c r="E122" s="171"/>
-      <c r="F122" s="171"/>
-    </row>
-    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="77" t="s">
-        <v>176</v>
-      </c>
-      <c r="B123" s="93">
-        <v>40000</v>
-      </c>
-      <c r="C123" s="82"/>
-      <c r="D123" s="171"/>
-      <c r="E123" s="181"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" s="77" t="s">
-        <v>142</v>
-      </c>
-      <c r="B124" s="168"/>
-      <c r="C124" s="82"/>
-      <c r="E124" s="108"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" s="77"/>
-      <c r="B125" s="168"/>
-      <c r="C125" s="82"/>
-      <c r="E125" s="108"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" s="100" t="s">
-        <v>29</v>
-      </c>
-      <c r="B126" s="101">
-        <f>SUM(B122:B125)</f>
-        <v>-312694.54000000004</v>
-      </c>
-      <c r="C126" s="82"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C127" s="83"/>
-      <c r="D127" s="171"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B128" s="80"/>
-      <c r="C128" s="76"/>
-    </row>
-    <row r="130" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="N130" s="12"/>
-    </row>
-    <row r="133" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B133" s="198"/>
-      <c r="C133" s="198"/>
-      <c r="D133" s="198"/>
-      <c r="E133" s="198"/>
-    </row>
-    <row r="134" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B134" s="198"/>
-      <c r="C134" s="198"/>
-      <c r="D134" s="198"/>
-      <c r="E134" s="198"/>
-    </row>
-    <row r="135" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B135" s="198"/>
-      <c r="C135" s="198"/>
-      <c r="D135" s="198"/>
-      <c r="E135" s="198"/>
-    </row>
-    <row r="136" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B136" s="198"/>
-      <c r="C136" s="198"/>
-      <c r="D136" s="198"/>
-      <c r="E136" s="198"/>
-    </row>
-    <row r="137" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B137" s="198"/>
-      <c r="C137" s="198"/>
-      <c r="D137" s="198"/>
-      <c r="E137" s="198"/>
+      <c r="B121" s="101">
+        <f>SUM(B117:B120)</f>
+        <v>-272694.54000000004</v>
+      </c>
+      <c r="C121" s="82"/>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C122" s="83"/>
+      <c r="D122" s="170"/>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B123" s="80"/>
+      <c r="C123" s="76"/>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N125" s="12"/>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B128" s="194"/>
+      <c r="C128" s="194"/>
+      <c r="D128" s="194"/>
+      <c r="E128" s="194"/>
+    </row>
+    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B129" s="194"/>
+      <c r="C129" s="194"/>
+      <c r="D129" s="194"/>
+      <c r="E129" s="194"/>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B130" s="194"/>
+      <c r="C130" s="194"/>
+      <c r="D130" s="194"/>
+      <c r="E130" s="194"/>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B131" s="194"/>
+      <c r="C131" s="194"/>
+      <c r="D131" s="194"/>
+      <c r="E131" s="194"/>
+    </row>
+    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B132" s="194"/>
+      <c r="C132" s="194"/>
+      <c r="D132" s="194"/>
+      <c r="E132" s="194"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B133:E137"/>
-    <mergeCell ref="D110:E115"/>
+  <mergeCells count="9">
+    <mergeCell ref="B128:E132"/>
+    <mergeCell ref="D105:E110"/>
     <mergeCell ref="B14:D17"/>
-    <mergeCell ref="A105:C105"/>
-    <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="A97:D97"/>
     <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A61:C61"/>
     <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A102:C102"/>
+    <mergeCell ref="A99:C99"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4144,26 +3970,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" customWidth="1"/>
-    <col min="6" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" customWidth="1"/>
+    <col min="6" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
-    <col min="14" max="14" width="13.6640625" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" customWidth="1"/>
-    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4180,17 +4006,17 @@
         <v>124</v>
       </c>
       <c r="L1" s="223">
-        <f>RESUMEN!D92</f>
-        <v>11708794.020000001</v>
+        <f>RESUMEN!D89</f>
+        <v>7000000</v>
       </c>
       <c r="M1" s="224"/>
       <c r="N1" s="148"/>
       <c r="O1" s="134">
         <f>L1*8.09%</f>
-        <v>947241.43621800013</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+        <v>566300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -4206,16 +4032,15 @@
       </c>
       <c r="L2" s="8"/>
       <c r="M2" s="148">
-        <f>8271670+8271670*15%+49000+4000-276</f>
-        <v>9565144.5</v>
+        <v>7000000</v>
       </c>
       <c r="N2" s="149"/>
       <c r="O2" s="134">
         <f>O1-K7-553-50-86-8</f>
-        <v>225448.75821800018</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+        <v>75279.750408999971</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="str">
         <f>RESUMEN!C5</f>
         <v>VTO: 15/10</v>
@@ -4234,13 +4059,13 @@
       </c>
       <c r="L3" s="8"/>
       <c r="M3" s="127">
-        <f>RESUMEN!D105</f>
-        <v>2916310.6</v>
+        <f>RESUMEN!D100</f>
+        <v>427050.4</v>
       </c>
       <c r="N3" s="147"/>
       <c r="O3" s="73"/>
     </row>
-    <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -4259,37 +4084,36 @@
       </c>
       <c r="L4" s="8"/>
       <c r="M4" s="127">
-        <f>3175000-2000+7</f>
-        <v>3173007</v>
+        <v>450000</v>
       </c>
       <c r="N4" s="123"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="220" t="s">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="216" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="234" t="s">
+      <c r="B5" s="218" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="220" t="s">
+      <c r="C5" s="216" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="232" t="s">
+      <c r="D5" s="220" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="220" t="s">
+      <c r="E5" s="216" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="220" t="s">
+      <c r="F5" s="216" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="220" t="s">
+      <c r="G5" s="216" t="s">
         <v>24</v>
       </c>
       <c r="H5" s="227" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="232" t="s">
+      <c r="I5" s="220" t="s">
         <v>108</v>
       </c>
       <c r="J5" s="225" t="s">
@@ -4308,23 +4132,23 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="221"/>
-      <c r="B6" s="235"/>
-      <c r="C6" s="221"/>
-      <c r="D6" s="236"/>
-      <c r="E6" s="221"/>
-      <c r="F6" s="221"/>
-      <c r="G6" s="221"/>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="217"/>
+      <c r="B6" s="219"/>
+      <c r="C6" s="217"/>
+      <c r="D6" s="221"/>
+      <c r="E6" s="217"/>
+      <c r="F6" s="217"/>
+      <c r="G6" s="217"/>
       <c r="H6" s="228"/>
-      <c r="I6" s="233"/>
+      <c r="I6" s="232"/>
       <c r="J6" s="226"/>
       <c r="K6" s="229"/>
       <c r="L6" s="231"/>
       <c r="M6" s="229"/>
       <c r="N6" s="226"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>33</v>
       </c>
@@ -4339,11 +4163,11 @@
         <v>8.09</v>
       </c>
       <c r="F7" s="88">
-        <v>614669.65776899992</v>
-      </c>
-      <c r="G7" s="196">
+        <v>957025.20554</v>
+      </c>
+      <c r="G7" s="192">
         <f>F7</f>
-        <v>614669.65776899992</v>
+        <v>957025.20554</v>
       </c>
       <c r="H7" s="130">
         <f>F7-G7</f>
@@ -4353,24 +4177,22 @@
         <v>12</v>
       </c>
       <c r="J7" s="88">
-        <v>235929.52754000001</v>
+        <v>34548.377359999999</v>
       </c>
       <c r="K7" s="88">
-        <v>721095.67799999996</v>
-      </c>
-      <c r="L7" s="98">
-        <v>0</v>
-      </c>
+        <v>490323.24959100003</v>
+      </c>
+      <c r="L7" s="98"/>
       <c r="M7" s="6">
         <f>K7+J7+H7+L7</f>
-        <v>957025.20554</v>
+        <v>524871.62695100007</v>
       </c>
       <c r="N7" s="11">
         <f>M7*6% + M7</f>
-        <v>1014446.7178724</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+        <v>556363.92456806009</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>35</v>
       </c>
@@ -4385,40 +4207,37 @@
         <v>2.21</v>
       </c>
       <c r="F8" s="88">
-        <v>181048.12201451589</v>
-      </c>
-      <c r="G8" s="196">
-        <v>180000</v>
+        <v>282561.27016451582</v>
+      </c>
+      <c r="G8" s="192">
+        <v>283000</v>
       </c>
       <c r="H8" s="130">
         <f t="shared" ref="H8:H51" si="0">F8-G8</f>
-        <v>1048.1220145158877</v>
+        <v>-438.72983548417687</v>
       </c>
       <c r="I8" s="106">
         <v>11</v>
       </c>
       <c r="J8" s="88">
         <f>M$4*E8%</f>
-        <v>70123.454699999987</v>
+        <v>9945</v>
       </c>
       <c r="K8" s="88">
         <f>M$2*E8 /100</f>
-        <v>211389.69344999999</v>
-      </c>
-      <c r="L8" s="160">
-        <f>J$3*E8%+J$4</f>
-        <v>0</v>
-      </c>
+        <v>154700</v>
+      </c>
+      <c r="L8" s="159"/>
       <c r="M8" s="6">
         <f>K8+J8+H8+L8</f>
-        <v>282561.27016451582</v>
+        <v>164206.27016451582</v>
       </c>
       <c r="N8" s="11">
         <f t="shared" ref="N8:N51" si="1">M8*6% + M8</f>
-        <v>299514.94637438678</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+        <v>174058.64637438676</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
@@ -4433,41 +4252,40 @@
         <v>4.21</v>
       </c>
       <c r="F9" s="88">
-        <v>348817.05528426333</v>
-      </c>
-      <c r="G9" s="197">
-        <f>392904-G34</f>
-        <v>348236.98199999996</v>
+        <v>536856.25143426331</v>
+      </c>
+      <c r="G9" s="193">
+        <f>605642-G34</f>
+        <v>536855.98190000001</v>
       </c>
       <c r="H9" s="130">
         <f t="shared" si="0"/>
-        <v>580.07328426337335</v>
+        <v>0.26953426329419017</v>
       </c>
       <c r="I9" s="106">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J9" s="88">
         <f t="shared" ref="J9:J51" si="2">M$4*E9%</f>
-        <v>133583.59469999999</v>
+        <v>18945</v>
       </c>
       <c r="K9" s="88">
         <f t="shared" ref="K9:K51" si="3">M$2*E9 /100</f>
-        <v>402692.58344999998</v>
-      </c>
-      <c r="L9" s="160">
-        <f t="shared" ref="L9:L50" si="4">J$3*E9%+J$4</f>
-        <v>0</v>
+        <v>294700</v>
+      </c>
+      <c r="L9" s="159">
+        <v>20000</v>
       </c>
       <c r="M9" s="6">
-        <f t="shared" ref="M9:M51" si="5">K9+J9+H9+L9</f>
-        <v>536856.25143426331</v>
+        <f t="shared" ref="M9:M51" si="4">K9+J9+H9+L9</f>
+        <v>333645.26953426329</v>
       </c>
       <c r="N9" s="11">
         <f t="shared" si="1"/>
-        <v>569067.62652031914</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+        <v>353663.9857063191</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>38</v>
       </c>
@@ -4482,40 +4300,38 @@
         <v>2.84</v>
       </c>
       <c r="F10" s="88">
-        <v>279110.11420596868</v>
-      </c>
-      <c r="G10" s="196">
-        <v>213555</v>
+        <v>427318.61680596869</v>
+      </c>
+      <c r="G10" s="192">
+        <f>F10</f>
+        <v>427318.61680596869</v>
       </c>
       <c r="H10" s="130">
         <f t="shared" si="0"/>
-        <v>65555.114205968683</v>
+        <v>0</v>
       </c>
       <c r="I10" s="106">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J10" s="88">
         <f t="shared" si="2"/>
-        <v>90113.398799999995</v>
+        <v>12780</v>
       </c>
       <c r="K10" s="88">
         <f t="shared" si="3"/>
-        <v>271650.10379999998</v>
-      </c>
-      <c r="L10" s="160">
+        <v>198800</v>
+      </c>
+      <c r="L10" s="159"/>
+      <c r="M10" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="6">
-        <f t="shared" si="5"/>
-        <v>427318.61680596869</v>
+        <v>211580</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="1"/>
-        <v>452957.73381432681</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+        <v>224274.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>38</v>
       </c>
@@ -4530,42 +4346,39 @@
         <v>3.43</v>
       </c>
       <c r="F11" s="88">
-        <v>283718.28100000002</v>
-      </c>
-      <c r="G11" s="196">
+        <v>436918.59645000001</v>
+      </c>
+      <c r="G11" s="192">
         <f>F11</f>
-        <v>283718.28100000002</v>
+        <v>436918.59645000001</v>
       </c>
       <c r="H11" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I11" s="106">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J11" s="88">
         <f t="shared" si="2"/>
-        <v>108834.14010000002</v>
+        <v>15435.000000000002</v>
       </c>
       <c r="K11" s="88">
         <f t="shared" si="3"/>
-        <v>328084.45634999999</v>
-      </c>
-      <c r="L11" s="160">
+        <v>240100</v>
+      </c>
+      <c r="L11" s="159"/>
+      <c r="M11" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="6">
-        <f t="shared" si="5"/>
-        <v>436918.59645000001</v>
+        <v>255535</v>
       </c>
       <c r="N11" s="11">
         <f t="shared" si="1"/>
-        <v>463133.712237</v>
+        <v>270867.09999999998</v>
       </c>
       <c r="P11" s="108"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>41</v>
       </c>
@@ -4580,11 +4393,11 @@
         <v>2.84</v>
       </c>
       <c r="F12" s="88">
-        <v>234915.42799999996</v>
-      </c>
-      <c r="G12" s="197">
+        <v>361763.50260000001</v>
+      </c>
+      <c r="G12" s="193">
         <f>F12</f>
-        <v>234915.42799999996</v>
+        <v>361763.50260000001</v>
       </c>
       <c r="H12" s="130">
         <f>F12-G12</f>
@@ -4595,26 +4408,23 @@
       </c>
       <c r="J12" s="88">
         <f t="shared" si="2"/>
-        <v>90113.398799999995</v>
+        <v>12780</v>
       </c>
       <c r="K12" s="88">
         <f t="shared" si="3"/>
-        <v>271650.10379999998</v>
-      </c>
-      <c r="L12" s="160">
+        <v>198800</v>
+      </c>
+      <c r="L12" s="159"/>
+      <c r="M12" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="6">
-        <f t="shared" si="5"/>
-        <v>361763.50260000001</v>
+        <v>211580</v>
       </c>
       <c r="N12" s="11">
         <f t="shared" si="1"/>
-        <v>383469.31275600003</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+        <v>224274.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>41</v>
       </c>
@@ -4629,40 +4439,40 @@
         <v>3.43</v>
       </c>
       <c r="F13" s="88">
-        <v>283718.82411924173</v>
-      </c>
-      <c r="G13" s="197">
-        <f>332521-G50</f>
-        <v>283718.147</v>
+        <v>446919.27356924175</v>
+      </c>
+      <c r="G13" s="193">
+        <f>444533-G50</f>
+        <v>369377.90615</v>
       </c>
       <c r="H13" s="130">
         <f t="shared" si="0"/>
-        <v>0.67711924173636362</v>
+        <v>77541.367419241753</v>
       </c>
       <c r="I13" s="106">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J13" s="88">
         <f t="shared" si="2"/>
-        <v>108834.14010000002</v>
+        <v>15435.000000000002</v>
       </c>
       <c r="K13" s="88">
         <f t="shared" si="3"/>
-        <v>328084.45634999999</v>
-      </c>
-      <c r="L13" s="160">
+        <v>240100</v>
+      </c>
+      <c r="L13" s="159">
         <v>10000</v>
       </c>
       <c r="M13" s="6">
-        <f t="shared" si="5"/>
-        <v>446919.27356924175</v>
+        <f t="shared" si="4"/>
+        <v>343076.36741924175</v>
       </c>
       <c r="N13" s="11">
         <f t="shared" si="1"/>
-        <v>473734.42998339626</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+        <v>363660.94946439628</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>43</v>
       </c>
@@ -4677,40 +4487,38 @@
         <v>2.84</v>
       </c>
       <c r="F14" s="88">
-        <v>258710.39332799998</v>
-      </c>
-      <c r="G14" s="196">
-        <v>234915</v>
+        <v>385558.89592799998</v>
+      </c>
+      <c r="G14" s="192">
+        <f>F14</f>
+        <v>385558.89592799998</v>
       </c>
       <c r="H14" s="130">
         <f t="shared" si="0"/>
-        <v>23795.393327999976</v>
+        <v>0</v>
       </c>
       <c r="I14" s="106">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J14" s="88">
         <f t="shared" si="2"/>
-        <v>90113.398799999995</v>
+        <v>12780</v>
       </c>
       <c r="K14" s="88">
         <f t="shared" si="3"/>
-        <v>271650.10379999998</v>
-      </c>
-      <c r="L14" s="160">
+        <v>198800</v>
+      </c>
+      <c r="L14" s="159"/>
+      <c r="M14" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M14" s="6">
-        <f t="shared" si="5"/>
-        <v>385558.89592799998</v>
+        <v>211580</v>
       </c>
       <c r="N14" s="11">
         <f t="shared" si="1"/>
-        <v>408692.42968368001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+        <v>224274.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>43</v>
       </c>
@@ -4725,41 +4533,38 @@
         <v>3.43</v>
       </c>
       <c r="F15" s="88">
-        <v>283718.16704653396</v>
-      </c>
-      <c r="G15" s="197">
-        <f>325076-G35</f>
-        <v>283717.65000000002</v>
+        <v>436919.11349653394</v>
+      </c>
+      <c r="G15" s="193">
+        <f>500609-G35</f>
+        <v>436918.24249999999</v>
       </c>
       <c r="H15" s="130">
         <f t="shared" si="0"/>
-        <v>0.51704653393244371</v>
+        <v>0.87099653395125642</v>
       </c>
       <c r="I15" s="106">
         <v>1</v>
       </c>
       <c r="J15" s="88">
         <f t="shared" si="2"/>
-        <v>108834.14010000002</v>
+        <v>15435.000000000002</v>
       </c>
       <c r="K15" s="88">
         <f t="shared" si="3"/>
-        <v>328084.45634999999</v>
-      </c>
-      <c r="L15" s="160">
+        <v>240100</v>
+      </c>
+      <c r="L15" s="159"/>
+      <c r="M15" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M15" s="6">
-        <f t="shared" si="5"/>
-        <v>436919.11349653394</v>
+        <v>255535.87099653395</v>
       </c>
       <c r="N15" s="11">
         <f t="shared" si="1"/>
-        <v>463134.26030632597</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+        <v>270868.02325632598</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>46</v>
       </c>
@@ -4774,41 +4579,38 @@
         <v>2.84</v>
       </c>
       <c r="F16" s="88">
-        <v>280282</v>
-      </c>
-      <c r="G16" s="197">
-        <f>275546+45267-G49</f>
-        <v>280281.81699999998</v>
+        <v>361763.68560000003</v>
+      </c>
+      <c r="G16" s="193">
+        <f>424181-G49</f>
+        <v>361764.05764999997</v>
       </c>
       <c r="H16" s="130">
         <f t="shared" si="0"/>
-        <v>0.18300000001909211</v>
+        <v>-0.37204999994719401</v>
       </c>
       <c r="I16" s="106">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J16" s="88">
         <f t="shared" si="2"/>
-        <v>90113.398799999995</v>
+        <v>12780</v>
       </c>
       <c r="K16" s="88">
         <f t="shared" si="3"/>
-        <v>271650.10379999998</v>
-      </c>
-      <c r="L16" s="160">
+        <v>198800</v>
+      </c>
+      <c r="L16" s="159"/>
+      <c r="M16" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="6">
-        <f t="shared" si="5"/>
-        <v>361763.68560000003</v>
+        <v>211579.62795000005</v>
       </c>
       <c r="N16" s="11">
         <f t="shared" si="1"/>
-        <v>383469.50673600001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+        <v>224274.40562700006</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>46</v>
       </c>
@@ -4823,40 +4625,40 @@
         <v>3.43</v>
       </c>
       <c r="F17" s="88">
-        <v>293717.14471111476</v>
-      </c>
-      <c r="G17" s="196">
-        <f>375606+1-G47-G48</f>
-        <v>293717.467</v>
+        <v>446918.27416111476</v>
+      </c>
+      <c r="G17" s="192">
+        <f>573026-G47-G48</f>
+        <v>446918.30015000002</v>
       </c>
       <c r="H17" s="130">
         <f t="shared" si="0"/>
-        <v>-0.32228888524696231</v>
+        <v>-2.5988885259721428E-2</v>
       </c>
       <c r="I17" s="106">
         <v>12</v>
       </c>
       <c r="J17" s="88">
         <f t="shared" si="2"/>
-        <v>108834.14010000002</v>
+        <v>15435.000000000002</v>
       </c>
       <c r="K17" s="88">
         <f t="shared" si="3"/>
-        <v>328084.45634999999</v>
-      </c>
-      <c r="L17" s="160">
+        <v>240100</v>
+      </c>
+      <c r="L17" s="159">
         <v>10000</v>
       </c>
       <c r="M17" s="6">
-        <f t="shared" si="5"/>
-        <v>446918.27416111476</v>
+        <f t="shared" si="4"/>
+        <v>265534.97401111474</v>
       </c>
       <c r="N17" s="11">
         <f t="shared" si="1"/>
-        <v>473733.37061078165</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+        <v>281467.0724517816</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>48</v>
       </c>
@@ -4871,41 +4673,38 @@
         <v>2.84</v>
       </c>
       <c r="F18" s="88">
-        <v>231604.94198325131</v>
-      </c>
-      <c r="G18" s="196">
-        <f>112000+160000+8000-G51</f>
-        <v>232851.481</v>
+        <v>360516.96358325134</v>
+      </c>
+      <c r="G18" s="192">
+        <f>320000+114000-G51</f>
+        <v>361392.53645000001</v>
       </c>
       <c r="H18" s="130">
         <f t="shared" si="0"/>
-        <v>-1246.5390167486912</v>
+        <v>-875.57286674866918</v>
       </c>
       <c r="I18" s="106">
         <v>12</v>
       </c>
       <c r="J18" s="88">
         <f t="shared" si="2"/>
-        <v>90113.398799999995</v>
+        <v>12780</v>
       </c>
       <c r="K18" s="88">
         <f t="shared" si="3"/>
-        <v>271650.10379999998</v>
-      </c>
-      <c r="L18" s="160">
+        <v>198800</v>
+      </c>
+      <c r="L18" s="159"/>
+      <c r="M18" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="6">
-        <f t="shared" si="5"/>
-        <v>360516.96358325134</v>
+        <v>210704.42713325133</v>
       </c>
       <c r="N18" s="11">
         <f t="shared" si="1"/>
-        <v>382147.98139824643</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+        <v>223346.69276124641</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>48</v>
       </c>
@@ -4920,41 +4719,38 @@
         <v>3.43</v>
       </c>
       <c r="F19" s="88">
-        <v>283718.85376516799</v>
-      </c>
-      <c r="G19" s="197">
-        <f>328385-G41</f>
-        <v>283717.98199999996</v>
+        <v>436919.46821516805</v>
+      </c>
+      <c r="G19" s="193">
+        <f>505705-G41</f>
+        <v>436918.98190000001</v>
       </c>
       <c r="H19" s="130">
         <f t="shared" si="0"/>
-        <v>0.87176516803447157</v>
+        <v>0.48631516803288832</v>
       </c>
       <c r="I19" s="106">
         <v>1</v>
       </c>
       <c r="J19" s="88">
         <f t="shared" si="2"/>
-        <v>108834.14010000002</v>
+        <v>15435.000000000002</v>
       </c>
       <c r="K19" s="88">
         <f t="shared" si="3"/>
-        <v>328084.45634999999</v>
-      </c>
-      <c r="L19" s="160">
+        <v>240100</v>
+      </c>
+      <c r="L19" s="159"/>
+      <c r="M19" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="6">
-        <f t="shared" si="5"/>
-        <v>436919.46821516805</v>
+        <v>255535.48631516803</v>
       </c>
       <c r="N19" s="11">
         <f t="shared" si="1"/>
-        <v>463134.63630807813</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+        <v>270867.61549407814</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
@@ -4969,41 +4765,38 @@
         <v>2.84</v>
       </c>
       <c r="F20" s="88">
-        <v>246161.02790707469</v>
-      </c>
-      <c r="G20" s="196">
-        <f>275446-G38</f>
-        <v>234914.81700000001</v>
+        <v>373009.71350707469</v>
+      </c>
+      <c r="G20" s="192">
+        <f>435427-G38</f>
+        <v>373010.05764999997</v>
       </c>
       <c r="H20" s="130">
         <f t="shared" si="0"/>
-        <v>11246.210907074681</v>
+        <v>-0.34414292528526857</v>
       </c>
       <c r="I20" s="106">
         <v>1</v>
       </c>
       <c r="J20" s="88">
         <f t="shared" si="2"/>
-        <v>90113.398799999995</v>
+        <v>12780</v>
       </c>
       <c r="K20" s="88">
         <f t="shared" si="3"/>
-        <v>271650.10379999998</v>
-      </c>
-      <c r="L20" s="160">
+        <v>198800</v>
+      </c>
+      <c r="L20" s="159"/>
+      <c r="M20" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="6">
-        <f t="shared" si="5"/>
-        <v>373009.71350707469</v>
+        <v>211579.65585707471</v>
       </c>
       <c r="N20" s="11">
         <f t="shared" si="1"/>
-        <v>395390.29631749919</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+        <v>224274.4352084992</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>51</v>
       </c>
@@ -5018,41 +4811,38 @@
         <v>3.43</v>
       </c>
       <c r="F21" s="88">
-        <v>283718.25609179586</v>
-      </c>
-      <c r="G21" s="196">
-        <f>328385-G45</f>
-        <v>283717.98199999996</v>
+        <v>436918.87054179591</v>
+      </c>
+      <c r="G21" s="192">
+        <f>505705-G45</f>
+        <v>436918.98190000001</v>
       </c>
       <c r="H21" s="130">
         <f t="shared" si="0"/>
-        <v>0.27409179590176791</v>
+        <v>-0.11135820409981534</v>
       </c>
       <c r="I21" s="106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" s="88">
         <f t="shared" si="2"/>
-        <v>108834.14010000002</v>
+        <v>15435.000000000002</v>
       </c>
       <c r="K21" s="88">
         <f t="shared" si="3"/>
-        <v>328084.45634999999</v>
-      </c>
-      <c r="L21" s="160">
+        <v>240100</v>
+      </c>
+      <c r="L21" s="159"/>
+      <c r="M21" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M21" s="6">
-        <f t="shared" si="5"/>
-        <v>436918.87054179591</v>
+        <v>255534.8886417959</v>
       </c>
       <c r="N21" s="11">
         <f t="shared" si="1"/>
-        <v>463134.00277430366</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+        <v>270866.98196030367</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>54</v>
       </c>
@@ -5060,48 +4850,45 @@
       <c r="C22" s="7">
         <v>38</v>
       </c>
-      <c r="D22" s="161" t="s">
+      <c r="D22" s="160" t="s">
         <v>128</v>
       </c>
       <c r="E22" s="7">
         <v>2.84</v>
       </c>
       <c r="F22" s="88">
-        <v>254915.42799999996</v>
-      </c>
-      <c r="G22" s="196">
+        <v>361763.50260000001</v>
+      </c>
+      <c r="G22" s="192">
         <f>F22</f>
-        <v>254915.42799999996</v>
+        <v>361763.50260000001</v>
       </c>
       <c r="H22" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I22" s="106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="88">
         <f t="shared" si="2"/>
-        <v>90113.398799999995</v>
+        <v>12780</v>
       </c>
       <c r="K22" s="88">
         <f t="shared" si="3"/>
-        <v>271650.10379999998</v>
-      </c>
-      <c r="L22" s="160">
+        <v>198800</v>
+      </c>
+      <c r="L22" s="159"/>
+      <c r="M22" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M22" s="6">
-        <f t="shared" si="5"/>
-        <v>361763.50260000001</v>
+        <v>211580</v>
       </c>
       <c r="N22" s="11">
         <f t="shared" si="1"/>
-        <v>383469.31275600003</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+        <v>224274.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>54</v>
       </c>
@@ -5116,40 +4903,40 @@
         <v>3.43</v>
       </c>
       <c r="F23" s="88">
-        <v>309550.97053314082</v>
-      </c>
-      <c r="G23" s="197">
-        <f>334000-G46</f>
-        <v>290160.14899999998</v>
+        <v>494287.98306212929</v>
+      </c>
+      <c r="G23" s="193">
+        <f>525000-G46</f>
+        <v>457487.79704999999</v>
       </c>
       <c r="H23" s="130">
         <f t="shared" si="0"/>
-        <v>19390.821533140843</v>
+        <v>36800.186012129299</v>
       </c>
       <c r="I23" s="106">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J23" s="88">
         <f t="shared" si="2"/>
-        <v>108834.14010000002</v>
+        <v>15435.000000000002</v>
       </c>
       <c r="K23" s="88">
         <f t="shared" si="3"/>
-        <v>328084.45634999999</v>
-      </c>
-      <c r="L23" s="160">
+        <v>240100</v>
+      </c>
+      <c r="L23" s="159">
         <v>10000</v>
       </c>
       <c r="M23" s="6">
-        <f t="shared" si="5"/>
-        <v>466309.41798314085</v>
+        <f t="shared" si="4"/>
+        <v>302335.1860121293</v>
       </c>
       <c r="N23" s="11">
         <f t="shared" si="1"/>
-        <v>494287.98306212929</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+        <v>320475.29717285704</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>56</v>
       </c>
@@ -5164,40 +4951,40 @@
         <v>2.84</v>
       </c>
       <c r="F24" s="88">
-        <v>233406.74547107471</v>
-      </c>
-      <c r="G24" s="196">
-        <f>266000+14000-G37</f>
-        <v>239468.81700000001</v>
+        <v>365701.43107107468</v>
+      </c>
+      <c r="G24" s="192">
+        <f>428118-G37</f>
+        <v>365701.05764999997</v>
       </c>
       <c r="H24" s="130">
         <f t="shared" si="0"/>
-        <v>-6062.0715289252985</v>
-      </c>
-      <c r="I24" s="172">
-        <v>6</v>
+        <v>0.37342107470612973</v>
+      </c>
+      <c r="I24" s="171">
+        <v>2</v>
       </c>
       <c r="J24" s="88">
         <f t="shared" si="2"/>
-        <v>90113.398799999995</v>
+        <v>12780</v>
       </c>
       <c r="K24" s="88">
         <f t="shared" si="3"/>
-        <v>271650.10379999998</v>
-      </c>
-      <c r="L24" s="160">
+        <v>198800</v>
+      </c>
+      <c r="L24" s="159">
         <v>10000</v>
       </c>
       <c r="M24" s="6">
-        <f t="shared" si="5"/>
-        <v>365701.43107107468</v>
+        <f t="shared" si="4"/>
+        <v>221580.37342107471</v>
       </c>
       <c r="N24" s="11">
         <f t="shared" si="1"/>
-        <v>387643.51693533914</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+        <v>234875.19582633919</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>56</v>
       </c>
@@ -5212,41 +4999,38 @@
         <v>3.43</v>
       </c>
       <c r="F25" s="88">
-        <v>322090.1091</v>
-      </c>
-      <c r="G25" s="196">
+        <v>436918.59645000001</v>
+      </c>
+      <c r="G25" s="192">
         <f>F25</f>
-        <v>322090.1091</v>
+        <v>436918.59645000001</v>
       </c>
       <c r="H25" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I25" s="106">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J25" s="88">
         <f t="shared" si="2"/>
-        <v>108834.14010000002</v>
+        <v>15435.000000000002</v>
       </c>
       <c r="K25" s="88">
         <f t="shared" si="3"/>
-        <v>328084.45634999999</v>
-      </c>
-      <c r="L25" s="160">
+        <v>240100</v>
+      </c>
+      <c r="L25" s="159"/>
+      <c r="M25" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M25" s="6">
-        <f t="shared" si="5"/>
-        <v>436918.59645000001</v>
+        <v>255535</v>
       </c>
       <c r="N25" s="11">
         <f t="shared" si="1"/>
-        <v>463133.712237</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+        <v>270867.09999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>59</v>
       </c>
@@ -5261,41 +5045,38 @@
         <v>6</v>
       </c>
       <c r="F26" s="88">
-        <v>496299.97081603704</v>
-      </c>
-      <c r="G26" s="197">
-        <f>676478.23-G30-G31-G36</f>
-        <v>544958.67700000003</v>
+        <v>715630.38381603709</v>
+      </c>
+      <c r="G26" s="193">
+        <f>1800000-G30-G31-G36</f>
+        <v>1597463.39115</v>
       </c>
       <c r="H26" s="131">
         <f t="shared" si="0"/>
-        <v>-48658.70618396299</v>
+        <v>-881833.00733396295</v>
       </c>
       <c r="I26" s="106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" s="88">
         <f t="shared" si="2"/>
-        <v>190380.41999999998</v>
+        <v>27000</v>
       </c>
       <c r="K26" s="88">
         <f t="shared" si="3"/>
-        <v>573908.67000000004</v>
-      </c>
-      <c r="L26" s="160">
+        <v>420000</v>
+      </c>
+      <c r="L26" s="159"/>
+      <c r="M26" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M26" s="6">
-        <f t="shared" si="5"/>
-        <v>715630.38381603709</v>
+        <v>-434833.00733396295</v>
       </c>
       <c r="N26" s="11">
         <f t="shared" si="1"/>
-        <v>758568.20684499934</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+        <v>-460922.98777400074</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>61</v>
       </c>
@@ -5310,41 +5091,38 @@
         <v>5.89</v>
       </c>
       <c r="F27" s="88">
-        <v>490962.31853526551</v>
-      </c>
-      <c r="G27" s="196">
-        <f>586914-G39-G40</f>
-        <v>490962.62800000003</v>
+        <v>750276.8138852655</v>
+      </c>
+      <c r="G27" s="192">
+        <f>898039-G39-G40</f>
+        <v>750276.44260000007</v>
       </c>
       <c r="H27" s="130">
         <f t="shared" si="0"/>
-        <v>-0.30946473451331258</v>
+        <v>0.3712852654280141</v>
       </c>
       <c r="I27" s="106">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J27" s="88">
         <f t="shared" si="2"/>
-        <v>186890.11229999998</v>
+        <v>26504.999999999996</v>
       </c>
       <c r="K27" s="88">
         <f t="shared" si="3"/>
-        <v>563387.01104999997</v>
-      </c>
-      <c r="L27" s="160">
+        <v>412300</v>
+      </c>
+      <c r="L27" s="159"/>
+      <c r="M27" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M27" s="6">
-        <f t="shared" si="5"/>
-        <v>750276.8138852655</v>
+        <v>438805.37128526543</v>
       </c>
       <c r="N27" s="11">
         <f t="shared" si="1"/>
-        <v>795293.42271838139</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+        <v>465133.69356238138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>63</v>
       </c>
@@ -5359,41 +5137,38 @@
         <v>5.89</v>
       </c>
       <c r="F28" s="88">
-        <v>510253.2765765409</v>
-      </c>
-      <c r="G28" s="196">
-        <f>598000-G32-G33</f>
-        <v>510320.29799999995</v>
+        <v>750210.10192654096</v>
+      </c>
+      <c r="G28" s="192">
+        <f>885235-G32-G33</f>
+        <v>750210.59409999999</v>
       </c>
       <c r="H28" s="130">
         <f t="shared" si="0"/>
-        <v>-67.02142345905304</v>
+        <v>-0.49217345903161913</v>
       </c>
       <c r="I28" s="106">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J28" s="88">
         <f t="shared" si="2"/>
-        <v>186890.11229999998</v>
+        <v>26504.999999999996</v>
       </c>
       <c r="K28" s="88">
         <f t="shared" si="3"/>
-        <v>563387.01104999997</v>
-      </c>
-      <c r="L28" s="160">
+        <v>412300</v>
+      </c>
+      <c r="L28" s="159"/>
+      <c r="M28" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M28" s="6">
-        <f t="shared" si="5"/>
-        <v>750210.10192654096</v>
+        <v>438804.50782654097</v>
       </c>
       <c r="N28" s="11">
         <f t="shared" si="1"/>
-        <v>795222.70804213337</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+        <v>465132.77829613345</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>65</v>
       </c>
@@ -5408,41 +5183,38 @@
         <v>5.89</v>
       </c>
       <c r="F29" s="88">
-        <v>815269.4544566999</v>
-      </c>
-      <c r="G29" s="197">
-        <f>950000-G42-G43-G44</f>
-        <v>816826.1129999999</v>
+        <v>748720.46480670001</v>
+      </c>
+      <c r="G29" s="193">
+        <f>954000-G42-G43-G44</f>
+        <v>748915.76084999996</v>
       </c>
       <c r="H29" s="131">
         <f t="shared" si="0"/>
-        <v>-1556.6585433</v>
+        <v>-195.29604329995345</v>
       </c>
       <c r="I29" s="106">
         <v>3</v>
       </c>
       <c r="J29" s="88">
         <f t="shared" si="2"/>
-        <v>186890.11229999998</v>
+        <v>26504.999999999996</v>
       </c>
       <c r="K29" s="88">
         <f t="shared" si="3"/>
-        <v>563387.01104999997</v>
-      </c>
-      <c r="L29" s="160">
+        <v>412300</v>
+      </c>
+      <c r="L29" s="159"/>
+      <c r="M29" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M29" s="6">
-        <f t="shared" si="5"/>
-        <v>748720.46480670001</v>
+        <v>438609.70395670005</v>
       </c>
       <c r="N29" s="11">
         <f t="shared" si="1"/>
-        <v>793643.69269510196</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+        <v>464926.28619410202</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="125" t="s">
         <v>96</v>
       </c>
@@ -5457,11 +5229,11 @@
         <v>0.54</v>
       </c>
       <c r="F30" s="88">
-        <v>44667.018000000011</v>
-      </c>
-      <c r="G30" s="196">
-        <f t="shared" ref="G30:G34" si="6">F30</f>
-        <v>44667.018000000011</v>
+        <v>68786.018100000016</v>
+      </c>
+      <c r="G30" s="192">
+        <f t="shared" ref="G30:G34" si="5">F30</f>
+        <v>68786.018100000016</v>
       </c>
       <c r="H30" s="130">
         <f t="shared" si="0"/>
@@ -5470,26 +5242,23 @@
       <c r="I30" s="106"/>
       <c r="J30" s="88">
         <f t="shared" si="2"/>
-        <v>17134.237800000003</v>
+        <v>2430</v>
       </c>
       <c r="K30" s="88">
         <f t="shared" si="3"/>
-        <v>51651.780300000006</v>
-      </c>
-      <c r="L30" s="160">
+        <v>37800.000000000007</v>
+      </c>
+      <c r="L30" s="159"/>
+      <c r="M30" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M30" s="6">
-        <f t="shared" si="5"/>
-        <v>68786.018100000016</v>
+        <v>40230.000000000007</v>
       </c>
       <c r="N30" s="11">
         <f t="shared" si="1"/>
-        <v>72913.179186000023</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+        <v>42643.80000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="125" t="s">
         <v>96</v>
       </c>
@@ -5504,11 +5273,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F31" s="88">
-        <v>45494.184999999998</v>
-      </c>
-      <c r="G31" s="196">
-        <f t="shared" si="6"/>
-        <v>45494.184999999998</v>
+        <v>70059.833250000011</v>
+      </c>
+      <c r="G31" s="192">
+        <f t="shared" si="5"/>
+        <v>70059.833250000011</v>
       </c>
       <c r="H31" s="130">
         <f t="shared" si="0"/>
@@ -5517,26 +5286,23 @@
       <c r="I31" s="106"/>
       <c r="J31" s="88">
         <f t="shared" si="2"/>
-        <v>17451.538500000002</v>
+        <v>2475.0000000000005</v>
       </c>
       <c r="K31" s="88">
         <f t="shared" si="3"/>
-        <v>52608.294750000008</v>
-      </c>
-      <c r="L31" s="160">
+        <v>38500.000000000007</v>
+      </c>
+      <c r="L31" s="159"/>
+      <c r="M31" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M31" s="6">
-        <f t="shared" si="5"/>
-        <v>70059.833250000011</v>
+        <v>40975.000000000007</v>
       </c>
       <c r="N31" s="11">
         <f t="shared" si="1"/>
-        <v>74263.423245000013</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+        <v>43433.500000000007</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="125" t="s">
         <v>96</v>
       </c>
@@ -5551,11 +5317,11 @@
         <v>0.45</v>
       </c>
       <c r="F32" s="88">
-        <v>37222.514999999999</v>
-      </c>
-      <c r="G32" s="196">
+        <v>57321.681750000003</v>
+      </c>
+      <c r="G32" s="192">
         <f>F32</f>
-        <v>37222.514999999999</v>
+        <v>57321.681750000003</v>
       </c>
       <c r="H32" s="130">
         <f t="shared" si="0"/>
@@ -5564,26 +5330,23 @@
       <c r="I32" s="106"/>
       <c r="J32" s="88">
         <f t="shared" si="2"/>
-        <v>14278.531500000001</v>
+        <v>2025.0000000000002</v>
       </c>
       <c r="K32" s="88">
         <f t="shared" si="3"/>
-        <v>43043.150250000006</v>
-      </c>
-      <c r="L32" s="160">
+        <v>31500</v>
+      </c>
+      <c r="L32" s="159"/>
+      <c r="M32" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M32" s="6">
-        <f t="shared" si="5"/>
-        <v>57321.681750000003</v>
+        <v>33525</v>
       </c>
       <c r="N32" s="11">
         <f t="shared" si="1"/>
-        <v>60760.982655</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+        <v>35536.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="125" t="s">
         <v>96</v>
       </c>
@@ -5598,11 +5361,11 @@
         <v>0.61</v>
       </c>
       <c r="F33" s="88">
-        <v>50457.187000000005</v>
-      </c>
-      <c r="G33" s="196">
-        <f t="shared" si="6"/>
-        <v>50457.187000000005</v>
+        <v>77702.724149999995</v>
+      </c>
+      <c r="G33" s="192">
+        <f t="shared" si="5"/>
+        <v>77702.724149999995</v>
       </c>
       <c r="H33" s="130">
         <f t="shared" si="0"/>
@@ -5611,26 +5374,23 @@
       <c r="I33" s="106"/>
       <c r="J33" s="88">
         <f t="shared" si="2"/>
-        <v>19355.342699999997</v>
+        <v>2745</v>
       </c>
       <c r="K33" s="88">
         <f t="shared" si="3"/>
-        <v>58347.381449999993</v>
-      </c>
-      <c r="L33" s="160">
+        <v>42700</v>
+      </c>
+      <c r="L33" s="159"/>
+      <c r="M33" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M33" s="6">
-        <f t="shared" si="5"/>
-        <v>77702.724149999995</v>
+        <v>45445</v>
       </c>
       <c r="N33" s="11">
         <f t="shared" si="1"/>
-        <v>82364.887598999994</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+        <v>48171.7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="125" t="s">
         <v>96</v>
       </c>
@@ -5645,11 +5405,11 @@
         <v>0.54</v>
       </c>
       <c r="F34" s="88">
-        <v>44667.018000000011</v>
-      </c>
-      <c r="G34" s="196">
-        <f t="shared" si="6"/>
-        <v>44667.018000000011</v>
+        <v>68786.018100000016</v>
+      </c>
+      <c r="G34" s="192">
+        <f t="shared" si="5"/>
+        <v>68786.018100000016</v>
       </c>
       <c r="H34" s="130">
         <f t="shared" si="0"/>
@@ -5658,26 +5418,23 @@
       <c r="I34" s="106"/>
       <c r="J34" s="88">
         <f t="shared" si="2"/>
-        <v>17134.237800000003</v>
+        <v>2430</v>
       </c>
       <c r="K34" s="88">
         <f t="shared" si="3"/>
-        <v>51651.780300000006</v>
-      </c>
-      <c r="L34" s="160">
+        <v>37800.000000000007</v>
+      </c>
+      <c r="L34" s="159"/>
+      <c r="M34" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M34" s="6">
-        <f t="shared" si="5"/>
-        <v>68786.018100000016</v>
+        <v>40230.000000000007</v>
       </c>
       <c r="N34" s="11">
         <f t="shared" si="1"/>
-        <v>72913.179186000023</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+        <v>42643.80000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="125" t="s">
         <v>96</v>
       </c>
@@ -5692,11 +5449,11 @@
         <v>0.5</v>
       </c>
       <c r="F35" s="11">
-        <v>41358.35</v>
-      </c>
-      <c r="G35" s="197">
+        <v>63690.757500000007</v>
+      </c>
+      <c r="G35" s="193">
         <f>F35</f>
-        <v>41358.35</v>
+        <v>63690.757500000007</v>
       </c>
       <c r="H35" s="130">
         <f t="shared" si="0"/>
@@ -5705,26 +5462,23 @@
       <c r="I35" s="106"/>
       <c r="J35" s="88">
         <f t="shared" si="2"/>
-        <v>15865.035</v>
+        <v>2250</v>
       </c>
       <c r="K35" s="88">
         <f t="shared" si="3"/>
-        <v>47825.722500000003</v>
-      </c>
-      <c r="L35" s="160">
+        <v>35000</v>
+      </c>
+      <c r="L35" s="159"/>
+      <c r="M35" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M35" s="6">
-        <f t="shared" si="5"/>
-        <v>63690.757500000007</v>
+        <v>37250</v>
       </c>
       <c r="N35" s="11">
         <f t="shared" si="1"/>
-        <v>67512.202950000006</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+        <v>39485</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="125" t="s">
         <v>96</v>
       </c>
@@ -5739,11 +5493,11 @@
         <v>0.5</v>
       </c>
       <c r="F36" s="88">
-        <v>41358.35</v>
-      </c>
-      <c r="G36" s="196">
-        <f t="shared" ref="G36:G41" si="7">F36</f>
-        <v>41358.35</v>
+        <v>63690.757500000007</v>
+      </c>
+      <c r="G36" s="192">
+        <f t="shared" ref="G36:G41" si="6">F36</f>
+        <v>63690.757500000007</v>
       </c>
       <c r="H36" s="130">
         <f t="shared" si="0"/>
@@ -5752,26 +5506,23 @@
       <c r="I36" s="106"/>
       <c r="J36" s="88">
         <f t="shared" si="2"/>
-        <v>15865.035</v>
+        <v>2250</v>
       </c>
       <c r="K36" s="88">
         <f t="shared" si="3"/>
-        <v>47825.722500000003</v>
-      </c>
-      <c r="L36" s="160">
+        <v>35000</v>
+      </c>
+      <c r="L36" s="159"/>
+      <c r="M36" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M36" s="6">
-        <f t="shared" si="5"/>
-        <v>63690.757500000007</v>
+        <v>37250</v>
       </c>
       <c r="N36" s="11">
         <f t="shared" si="1"/>
-        <v>67512.202950000006</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+        <v>39485</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="125" t="s">
         <v>96</v>
       </c>
@@ -5786,11 +5537,11 @@
         <v>0.49</v>
       </c>
       <c r="F37" s="88">
-        <v>40531.182999999997</v>
-      </c>
-      <c r="G37" s="196">
-        <f t="shared" si="7"/>
-        <v>40531.182999999997</v>
+        <v>62416.942349999998</v>
+      </c>
+      <c r="G37" s="192">
+        <f t="shared" si="6"/>
+        <v>62416.942349999998</v>
       </c>
       <c r="H37" s="130">
         <f t="shared" si="0"/>
@@ -5799,26 +5550,23 @@
       <c r="I37" s="106"/>
       <c r="J37" s="88">
         <f t="shared" si="2"/>
-        <v>15547.7343</v>
+        <v>2205</v>
       </c>
       <c r="K37" s="88">
         <f t="shared" si="3"/>
-        <v>46869.208049999994</v>
-      </c>
-      <c r="L37" s="160">
+        <v>34300</v>
+      </c>
+      <c r="L37" s="159"/>
+      <c r="M37" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M37" s="6">
-        <f t="shared" si="5"/>
-        <v>62416.942349999998</v>
+        <v>36505</v>
       </c>
       <c r="N37" s="11">
         <f t="shared" si="1"/>
-        <v>66161.958891000002</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+        <v>38695.300000000003</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="125" t="s">
         <v>96</v>
       </c>
@@ -5833,11 +5581,11 @@
         <v>0.49</v>
       </c>
       <c r="F38" s="88">
-        <v>40531.182999999997</v>
-      </c>
-      <c r="G38" s="196">
-        <f t="shared" si="7"/>
-        <v>40531.182999999997</v>
+        <v>62416.942349999998</v>
+      </c>
+      <c r="G38" s="192">
+        <f t="shared" si="6"/>
+        <v>62416.942349999998</v>
       </c>
       <c r="H38" s="130">
         <f t="shared" si="0"/>
@@ -5846,26 +5594,23 @@
       <c r="I38" s="106"/>
       <c r="J38" s="88">
         <f t="shared" si="2"/>
-        <v>15547.7343</v>
+        <v>2205</v>
       </c>
       <c r="K38" s="88">
         <f t="shared" si="3"/>
-        <v>46869.208049999994</v>
-      </c>
-      <c r="L38" s="160">
+        <v>34300</v>
+      </c>
+      <c r="L38" s="159"/>
+      <c r="M38" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M38" s="6">
-        <f t="shared" si="5"/>
-        <v>62416.942349999998</v>
+        <v>36505</v>
       </c>
       <c r="N38" s="11">
         <f t="shared" si="1"/>
-        <v>66161.958891000002</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+        <v>38695.300000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="125" t="s">
         <v>96</v>
       </c>
@@ -5880,11 +5625,11 @@
         <v>0.59</v>
       </c>
       <c r="F39" s="88">
-        <v>48802.852999999996</v>
-      </c>
-      <c r="G39" s="196">
-        <f t="shared" si="7"/>
-        <v>48802.852999999996</v>
+        <v>75155.09384999999</v>
+      </c>
+      <c r="G39" s="192">
+        <f t="shared" si="6"/>
+        <v>75155.09384999999</v>
       </c>
       <c r="H39" s="130">
         <f t="shared" si="0"/>
@@ -5893,26 +5638,23 @@
       <c r="I39" s="106"/>
       <c r="J39" s="88">
         <f t="shared" si="2"/>
-        <v>18720.741299999998</v>
+        <v>2655</v>
       </c>
       <c r="K39" s="88">
         <f t="shared" si="3"/>
-        <v>56434.352549999996</v>
-      </c>
-      <c r="L39" s="160">
+        <v>41300</v>
+      </c>
+      <c r="L39" s="159"/>
+      <c r="M39" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M39" s="6">
-        <f t="shared" si="5"/>
-        <v>75155.09384999999</v>
+        <v>43955</v>
       </c>
       <c r="N39" s="11">
         <f t="shared" si="1"/>
-        <v>79664.399480999986</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+        <v>46592.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="125" t="s">
         <v>96</v>
       </c>
@@ -5927,11 +5669,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F40" s="88">
-        <v>47148.518999999993</v>
-      </c>
-      <c r="G40" s="196">
-        <f t="shared" si="7"/>
-        <v>47148.518999999993</v>
+        <v>72607.463549999986</v>
+      </c>
+      <c r="G40" s="192">
+        <f t="shared" si="6"/>
+        <v>72607.463549999986</v>
       </c>
       <c r="H40" s="130">
         <f t="shared" si="0"/>
@@ -5940,26 +5682,23 @@
       <c r="I40" s="106"/>
       <c r="J40" s="88">
         <f t="shared" si="2"/>
-        <v>18086.139899999998</v>
+        <v>2564.9999999999995</v>
       </c>
       <c r="K40" s="88">
         <f t="shared" si="3"/>
-        <v>54521.323649999991</v>
-      </c>
-      <c r="L40" s="160">
+        <v>39899.999999999993</v>
+      </c>
+      <c r="L40" s="159"/>
+      <c r="M40" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M40" s="6">
-        <f t="shared" si="5"/>
-        <v>72607.463549999986</v>
+        <v>42464.999999999993</v>
       </c>
       <c r="N40" s="11">
         <f t="shared" si="1"/>
-        <v>76963.911362999992</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+        <v>45012.899999999994</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="125" t="s">
         <v>96</v>
       </c>
@@ -5974,11 +5713,11 @@
         <v>0.54</v>
       </c>
       <c r="F41" s="88">
-        <v>44667.018000000011</v>
-      </c>
-      <c r="G41" s="196">
-        <f t="shared" si="7"/>
-        <v>44667.018000000011</v>
+        <v>68786.018100000016</v>
+      </c>
+      <c r="G41" s="192">
+        <f t="shared" si="6"/>
+        <v>68786.018100000016</v>
       </c>
       <c r="H41" s="130">
         <f t="shared" si="0"/>
@@ -5987,26 +5726,23 @@
       <c r="I41" s="106"/>
       <c r="J41" s="88">
         <f t="shared" si="2"/>
-        <v>17134.237800000003</v>
+        <v>2430</v>
       </c>
       <c r="K41" s="88">
         <f t="shared" si="3"/>
-        <v>51651.780300000006</v>
-      </c>
-      <c r="L41" s="160">
+        <v>37800.000000000007</v>
+      </c>
+      <c r="L41" s="159"/>
+      <c r="M41" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M41" s="6">
-        <f t="shared" si="5"/>
-        <v>68786.018100000016</v>
+        <v>40230.000000000007</v>
       </c>
       <c r="N41" s="11">
         <f t="shared" si="1"/>
-        <v>72913.179186000023</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+        <v>42643.80000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="125" t="s">
         <v>96</v>
       </c>
@@ -6021,11 +5757,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F42" s="88">
-        <v>45494.184999999998</v>
-      </c>
-      <c r="G42" s="196">
+        <v>70059.833250000011</v>
+      </c>
+      <c r="G42" s="192">
         <f>F42</f>
-        <v>45494.184999999998</v>
+        <v>70059.833250000011</v>
       </c>
       <c r="H42" s="130">
         <f t="shared" si="0"/>
@@ -6034,26 +5770,23 @@
       <c r="I42" s="106"/>
       <c r="J42" s="88">
         <f t="shared" si="2"/>
-        <v>17451.538500000002</v>
+        <v>2475.0000000000005</v>
       </c>
       <c r="K42" s="88">
         <f t="shared" si="3"/>
-        <v>52608.294750000008</v>
-      </c>
-      <c r="L42" s="160">
+        <v>38500.000000000007</v>
+      </c>
+      <c r="L42" s="159"/>
+      <c r="M42" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M42" s="6">
-        <f t="shared" si="5"/>
-        <v>70059.833250000011</v>
+        <v>40975.000000000007</v>
       </c>
       <c r="N42" s="11">
         <f t="shared" si="1"/>
-        <v>74263.423245000013</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+        <v>43433.500000000007</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="125" t="s">
         <v>96</v>
       </c>
@@ -6068,11 +5801,11 @@
         <v>0.45</v>
       </c>
       <c r="F43" s="88">
-        <v>37222.514999999999</v>
-      </c>
-      <c r="G43" s="196">
-        <f t="shared" ref="G43:G44" si="8">F43</f>
-        <v>37222.514999999999</v>
+        <v>57321.681750000003</v>
+      </c>
+      <c r="G43" s="192">
+        <f t="shared" ref="G43:G44" si="7">F43</f>
+        <v>57321.681750000003</v>
       </c>
       <c r="H43" s="130">
         <f t="shared" si="0"/>
@@ -6081,30 +5814,27 @@
       <c r="I43" s="106"/>
       <c r="J43" s="88">
         <f t="shared" si="2"/>
-        <v>14278.531500000001</v>
+        <v>2025.0000000000002</v>
       </c>
       <c r="K43" s="88">
         <f t="shared" si="3"/>
-        <v>43043.150250000006</v>
-      </c>
-      <c r="L43" s="160">
+        <v>31500</v>
+      </c>
+      <c r="L43" s="159"/>
+      <c r="M43" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M43" s="6">
-        <f t="shared" si="5"/>
-        <v>57321.681750000003</v>
+        <v>33525</v>
       </c>
       <c r="N43" s="11">
         <f t="shared" si="1"/>
-        <v>60760.982655</v>
+        <v>35536.5</v>
       </c>
       <c r="P43" s="108">
         <f>L1-K52</f>
-        <v>2196374.0320500005</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+        <v>75976.750408999622</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="125" t="s">
         <v>96</v>
       </c>
@@ -6119,11 +5849,11 @@
         <v>0.61</v>
       </c>
       <c r="F44" s="88">
-        <v>50457.187000000005</v>
-      </c>
-      <c r="G44" s="196">
-        <f t="shared" si="8"/>
-        <v>50457.187000000005</v>
+        <v>77702.724149999995</v>
+      </c>
+      <c r="G44" s="192">
+        <f t="shared" si="7"/>
+        <v>77702.724149999995</v>
       </c>
       <c r="H44" s="130">
         <f t="shared" si="0"/>
@@ -6132,26 +5862,23 @@
       <c r="I44" s="106"/>
       <c r="J44" s="88">
         <f t="shared" si="2"/>
-        <v>19355.342699999997</v>
+        <v>2745</v>
       </c>
       <c r="K44" s="88">
         <f t="shared" si="3"/>
-        <v>58347.381449999993</v>
-      </c>
-      <c r="L44" s="160">
+        <v>42700</v>
+      </c>
+      <c r="L44" s="159"/>
+      <c r="M44" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M44" s="6">
-        <f t="shared" si="5"/>
-        <v>77702.724149999995</v>
+        <v>45445</v>
       </c>
       <c r="N44" s="11">
         <f t="shared" si="1"/>
-        <v>82364.887598999994</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+        <v>48171.7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="125" t="s">
         <v>96</v>
       </c>
@@ -6166,11 +5893,11 @@
         <v>0.54</v>
       </c>
       <c r="F45" s="88">
-        <v>44667.018000000011</v>
-      </c>
-      <c r="G45" s="196">
-        <f t="shared" ref="G45:G51" si="9">F45</f>
-        <v>44667.018000000011</v>
+        <v>68786.018100000016</v>
+      </c>
+      <c r="G45" s="192">
+        <f t="shared" ref="G45:G51" si="8">F45</f>
+        <v>68786.018100000016</v>
       </c>
       <c r="H45" s="130">
         <f t="shared" si="0"/>
@@ -6179,26 +5906,23 @@
       <c r="I45" s="106"/>
       <c r="J45" s="88">
         <f t="shared" si="2"/>
-        <v>17134.237800000003</v>
+        <v>2430</v>
       </c>
       <c r="K45" s="88">
         <f t="shared" si="3"/>
-        <v>51651.780300000006</v>
-      </c>
-      <c r="L45" s="160">
+        <v>37800.000000000007</v>
+      </c>
+      <c r="L45" s="159"/>
+      <c r="M45" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M45" s="6">
-        <f t="shared" si="5"/>
-        <v>68786.018100000016</v>
+        <v>40230.000000000007</v>
       </c>
       <c r="N45" s="11">
         <f t="shared" si="1"/>
-        <v>72913.179186000023</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+        <v>42643.80000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="125" t="s">
         <v>96</v>
       </c>
@@ -6213,11 +5937,11 @@
         <v>0.5</v>
       </c>
       <c r="F46" s="88">
-        <v>43839.850999999995</v>
-      </c>
-      <c r="G46" s="196">
+        <v>67512.202950000006</v>
+      </c>
+      <c r="G46" s="192">
         <f>F46</f>
-        <v>43839.850999999995</v>
+        <v>67512.202950000006</v>
       </c>
       <c r="H46" s="130">
         <f t="shared" si="0"/>
@@ -6226,29 +5950,26 @@
       <c r="I46" s="106"/>
       <c r="J46" s="88">
         <f t="shared" si="2"/>
-        <v>15865.035</v>
+        <v>2250</v>
       </c>
       <c r="K46" s="88">
         <f t="shared" si="3"/>
-        <v>47825.722500000003</v>
-      </c>
-      <c r="L46" s="160">
+        <v>35000</v>
+      </c>
+      <c r="L46" s="159"/>
+      <c r="M46" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M46" s="6">
-        <f t="shared" si="5"/>
-        <v>63690.757500000007</v>
+        <v>37250</v>
       </c>
       <c r="N46" s="11">
         <f t="shared" si="1"/>
-        <v>67512.202950000006</v>
+        <v>39485</v>
       </c>
       <c r="Q46" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="125" t="s">
         <v>96</v>
       </c>
@@ -6263,11 +5984,11 @@
         <v>0.5</v>
       </c>
       <c r="F47" s="88">
-        <v>41358.35</v>
-      </c>
-      <c r="G47" s="196">
-        <f t="shared" si="9"/>
-        <v>41358.35</v>
+        <v>63690.757500000007</v>
+      </c>
+      <c r="G47" s="192">
+        <f t="shared" si="8"/>
+        <v>63690.757500000007</v>
       </c>
       <c r="H47" s="130">
         <f t="shared" si="0"/>
@@ -6276,31 +5997,28 @@
       <c r="I47" s="106"/>
       <c r="J47" s="88">
         <f t="shared" si="2"/>
-        <v>15865.035</v>
+        <v>2250</v>
       </c>
       <c r="K47" s="88">
         <f t="shared" si="3"/>
-        <v>47825.722500000003</v>
-      </c>
-      <c r="L47" s="160">
+        <v>35000</v>
+      </c>
+      <c r="L47" s="159"/>
+      <c r="M47" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M47" s="6">
-        <f t="shared" si="5"/>
-        <v>63690.757500000007</v>
+        <v>37250</v>
       </c>
       <c r="N47" s="11">
         <f t="shared" si="1"/>
-        <v>67512.202950000006</v>
+        <v>39485</v>
       </c>
       <c r="O47" s="137"/>
       <c r="Q47" s="134">
         <f>M3-J52</f>
-        <v>-0.13370000058785081</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+        <v>13455.400000000023</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="125" t="s">
         <v>96</v>
       </c>
@@ -6315,11 +6033,11 @@
         <v>0.49</v>
       </c>
       <c r="F48" s="88">
-        <v>40531.182999999997</v>
-      </c>
-      <c r="G48" s="196">
-        <f t="shared" si="9"/>
-        <v>40531.182999999997</v>
+        <v>62416.942349999998</v>
+      </c>
+      <c r="G48" s="192">
+        <f t="shared" si="8"/>
+        <v>62416.942349999998</v>
       </c>
       <c r="H48" s="130">
         <f t="shared" si="0"/>
@@ -6328,26 +6046,23 @@
       <c r="I48" s="106"/>
       <c r="J48" s="88">
         <f t="shared" si="2"/>
-        <v>15547.7343</v>
+        <v>2205</v>
       </c>
       <c r="K48" s="88">
         <f t="shared" si="3"/>
-        <v>46869.208049999994</v>
-      </c>
-      <c r="L48" s="160">
+        <v>34300</v>
+      </c>
+      <c r="L48" s="159"/>
+      <c r="M48" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M48" s="6">
-        <f t="shared" si="5"/>
-        <v>62416.942349999998</v>
+        <v>36505</v>
       </c>
       <c r="N48" s="11">
         <f t="shared" si="1"/>
-        <v>66161.958891000002</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+        <v>38695.300000000003</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="125" t="s">
         <v>96</v>
       </c>
@@ -6363,11 +6078,11 @@
         <v>0.49</v>
       </c>
       <c r="F49" s="88">
-        <v>40531.182999999997</v>
-      </c>
-      <c r="G49" s="196">
+        <v>62416.942349999998</v>
+      </c>
+      <c r="G49" s="192">
         <f>F49</f>
-        <v>40531.182999999997</v>
+        <v>62416.942349999998</v>
       </c>
       <c r="H49" s="130">
         <f t="shared" si="0"/>
@@ -6376,26 +6091,23 @@
       <c r="I49" s="106"/>
       <c r="J49" s="88">
         <f t="shared" si="2"/>
-        <v>15547.7343</v>
+        <v>2205</v>
       </c>
       <c r="K49" s="88">
         <f t="shared" si="3"/>
-        <v>46869.208049999994</v>
-      </c>
-      <c r="L49" s="160">
+        <v>34300</v>
+      </c>
+      <c r="L49" s="159"/>
+      <c r="M49" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M49" s="6">
-        <f t="shared" si="5"/>
-        <v>62416.942349999998</v>
+        <v>36505</v>
       </c>
       <c r="N49" s="11">
         <f t="shared" si="1"/>
-        <v>66161.958891000002</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+        <v>38695.300000000003</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="125" t="s">
         <v>96</v>
       </c>
@@ -6410,11 +6122,11 @@
         <v>0.59</v>
       </c>
       <c r="F50" s="88">
-        <v>48802.852999999996</v>
-      </c>
-      <c r="G50" s="197">
+        <v>75155.09384999999</v>
+      </c>
+      <c r="G50" s="193">
         <f>F50</f>
-        <v>48802.852999999996</v>
+        <v>75155.09384999999</v>
       </c>
       <c r="H50" s="130">
         <f t="shared" si="0"/>
@@ -6423,26 +6135,23 @@
       <c r="I50" s="106"/>
       <c r="J50" s="88">
         <f t="shared" si="2"/>
-        <v>18720.741299999998</v>
+        <v>2655</v>
       </c>
       <c r="K50" s="88">
         <f t="shared" si="3"/>
-        <v>56434.352549999996</v>
-      </c>
-      <c r="L50" s="160">
+        <v>41300</v>
+      </c>
+      <c r="L50" s="159"/>
+      <c r="M50" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M50" s="6">
-        <f t="shared" si="5"/>
-        <v>75155.09384999999</v>
+        <v>43955</v>
       </c>
       <c r="N50" s="11">
         <f t="shared" si="1"/>
-        <v>79664.399480999986</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+        <v>46592.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="125" t="s">
         <v>96</v>
       </c>
@@ -6457,11 +6166,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F51" s="88">
-        <v>47148.518999999993</v>
-      </c>
-      <c r="G51" s="196">
-        <f t="shared" si="9"/>
-        <v>47148.518999999993</v>
+        <v>72607.463549999986</v>
+      </c>
+      <c r="G51" s="192">
+        <f t="shared" si="8"/>
+        <v>72607.463549999986</v>
       </c>
       <c r="H51" s="130">
         <f t="shared" si="0"/>
@@ -6470,26 +6179,23 @@
       <c r="I51" s="106"/>
       <c r="J51" s="88">
         <f t="shared" si="2"/>
-        <v>18086.139899999998</v>
+        <v>2564.9999999999995</v>
       </c>
       <c r="K51" s="88">
         <f t="shared" si="3"/>
-        <v>54521.323649999991</v>
-      </c>
-      <c r="L51" s="160">
-        <f t="shared" ref="L51" si="10">J$3*E51%+J$4</f>
-        <v>0</v>
-      </c>
+        <v>39899.999999999993</v>
+      </c>
+      <c r="L51" s="159"/>
       <c r="M51" s="6">
-        <f t="shared" si="5"/>
-        <v>72607.463549999986</v>
+        <f t="shared" si="4"/>
+        <v>42464.999999999993</v>
       </c>
       <c r="N51" s="11">
         <f t="shared" si="1"/>
-        <v>76963.911362999992</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>45012.899999999994</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="89"/>
       <c r="B52" s="89"/>
       <c r="C52" s="89"/>
@@ -6498,45 +6204,45 @@
         <f>SUM(E7:E51)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="F52" s="90">
+      <c r="F52" s="244">
         <f>SUM(F7:F51)</f>
-        <v>8787334.7637146879</v>
-      </c>
-      <c r="G52" s="90">
+        <v>12800486.88956468</v>
+      </c>
+      <c r="G52" s="244">
         <f>SUM(G7:G51)</f>
-        <v>8723308.1338689979</v>
+        <v>13569486.916373972</v>
       </c>
       <c r="H52" s="89"/>
       <c r="I52" s="89"/>
       <c r="J52" s="126">
         <f>SUM(J8:J51)</f>
-        <v>2916310.7337000007</v>
+        <v>413595</v>
       </c>
       <c r="K52" s="90">
         <f>SUM(K7:K51)</f>
-        <v>9512419.9879500009</v>
-      </c>
-      <c r="L52" s="167">
+        <v>6924023.2495910004</v>
+      </c>
+      <c r="L52" s="166">
         <f>SUM(L7:L51)</f>
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="M52" s="91">
         <f>SUM(M7:M51)</f>
-        <v>12768686.879035691</v>
+        <v>6663166.6001417069</v>
       </c>
       <c r="N52" s="90">
         <f>SUM(N7:N51)</f>
-        <v>13534808.091777833</v>
+        <v>7062956.5961502092</v>
       </c>
       <c r="P52" s="134"/>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="K53" s="137">
         <f>K52-L1</f>
-        <v>-2196374.0320500005</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>-75976.750408999622</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C54" s="222"/>
       <c r="D54" s="222"/>
       <c r="E54" s="222"/>
@@ -6550,7 +6256,7 @@
       <c r="M54" s="222"/>
       <c r="N54" s="222"/>
     </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="C55" s="222"/>
       <c r="D55" s="222"/>
       <c r="E55" s="222"/>
@@ -6564,21 +6270,21 @@
       <c r="M55" s="222"/>
       <c r="N55" s="222"/>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C56" s="162"/>
-      <c r="D56" s="162"/>
-      <c r="E56" s="162"/>
-      <c r="F56" s="162"/>
-      <c r="G56" s="162"/>
-      <c r="H56" s="162"/>
-      <c r="I56" s="162"/>
-      <c r="J56" s="162"/>
-      <c r="K56" s="162"/>
-      <c r="L56" s="162"/>
-      <c r="M56" s="162"/>
-      <c r="N56" s="162"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C56" s="161"/>
+      <c r="D56" s="161"/>
+      <c r="E56" s="161"/>
+      <c r="F56" s="161"/>
+      <c r="G56" s="161"/>
+      <c r="H56" s="161"/>
+      <c r="I56" s="161"/>
+      <c r="J56" s="161"/>
+      <c r="K56" s="161"/>
+      <c r="L56" s="161"/>
+      <c r="M56" s="161"/>
+      <c r="N56" s="161"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C57" s="222" t="s">
         <v>129</v>
       </c>
@@ -6594,7 +6300,7 @@
       <c r="M57" s="222"/>
       <c r="N57" s="222"/>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C58" s="222"/>
       <c r="D58" s="222"/>
       <c r="E58" s="222"/>
@@ -6608,7 +6314,7 @@
       <c r="M58" s="222"/>
       <c r="N58" s="222"/>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C59" s="222"/>
       <c r="D59" s="222"/>
       <c r="E59" s="222"/>
@@ -6622,7 +6328,7 @@
       <c r="M59" s="222"/>
       <c r="N59" s="222"/>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C60" s="222"/>
       <c r="D60" s="222"/>
       <c r="E60" s="222"/>
@@ -6636,7 +6342,7 @@
       <c r="M60" s="222"/>
       <c r="N60" s="222"/>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C61" s="222"/>
       <c r="D61" s="222"/>
       <c r="E61" s="222"/>
@@ -6650,7 +6356,7 @@
       <c r="M61" s="222"/>
       <c r="N61" s="222"/>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C62" s="222"/>
       <c r="D62" s="222"/>
       <c r="E62" s="222"/>
@@ -6664,7 +6370,7 @@
       <c r="M62" s="222"/>
       <c r="N62" s="222"/>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C63" s="222"/>
       <c r="D63" s="222"/>
       <c r="E63" s="222"/>
@@ -6680,11 +6386,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
@@ -6697,6 +6398,11 @@
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="I5:I6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -6706,88 +6412,88 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{596D2FF5-218B-41A1-9BCB-F43114942886}">
   <dimension ref="C4:H25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="14.88671875" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C4" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" s="183">
+        <v>-447223.45918396302</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C5" t="s">
+      <c r="D6" s="183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
         <v>146</v>
       </c>
-      <c r="D5" s="184">
-        <v>-447223.45918396302</v>
-      </c>
-    </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C6" t="s">
+      <c r="D7" s="183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
         <v>147</v>
       </c>
-      <c r="D6" s="184">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C7" t="s">
+      <c r="D8" s="183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C10" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" s="183">
+        <v>451182</v>
+      </c>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>145</v>
+      </c>
+      <c r="D12" s="183">
+        <v>40606.380000000005</v>
+      </c>
+    </row>
+    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>146</v>
+      </c>
+      <c r="D13" s="183">
+        <v>41358.350000000006</v>
+      </c>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D14" s="183">
+        <v>37598.5</v>
+      </c>
+    </row>
+    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C16" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="D7" s="184">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C8" t="s">
-        <v>149</v>
-      </c>
-      <c r="D8" s="184">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C10" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C11" t="s">
-        <v>146</v>
-      </c>
-      <c r="D11" s="184">
-        <v>451182</v>
-      </c>
-    </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C12" t="s">
-        <v>147</v>
-      </c>
-      <c r="D12" s="184">
-        <v>40606.380000000005</v>
-      </c>
-    </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C13" t="s">
-        <v>148</v>
-      </c>
-      <c r="D13" s="184">
-        <v>41358.350000000006</v>
-      </c>
-    </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C14" t="s">
-        <v>149</v>
-      </c>
-      <c r="D14" s="184">
-        <v>37598.5</v>
-      </c>
-    </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C16" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6795,67 +6501,67 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>146</v>
-      </c>
-      <c r="D17" s="184">
+        <v>144</v>
+      </c>
+      <c r="D17" s="183">
         <f>D11+D5</f>
         <v>3958.5408160369843</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
+        <v>145</v>
+      </c>
+      <c r="D18" s="183">
+        <v>40606.380000000005</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" s="183">
+        <v>41358.350000000006</v>
+      </c>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
         <v>147</v>
       </c>
-      <c r="D18" s="184">
-        <v>40606.380000000005</v>
-      </c>
-    </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C19" t="s">
-        <v>148</v>
-      </c>
-      <c r="D19" s="184">
-        <v>41358.350000000006</v>
-      </c>
-    </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C20" t="s">
-        <v>149</v>
-      </c>
-      <c r="D20" s="184">
+      <c r="D20" s="183">
         <v>37598.5</v>
       </c>
     </row>
-    <row r="21" spans="3:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
-        <v>153</v>
-      </c>
-      <c r="D21" s="184">
+        <v>151</v>
+      </c>
+      <c r="D21" s="183">
         <v>-25000</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C22" s="237" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="240">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C22" s="233" t="s">
+        <v>150</v>
+      </c>
+      <c r="D22" s="236">
         <f>SUM(D17:D21)</f>
         <v>98521.770816036995</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C23" s="238"/>
-      <c r="D23" s="241"/>
-    </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C24" s="238"/>
-      <c r="D24" s="241"/>
-    </row>
-    <row r="25" spans="3:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C25" s="239"/>
-      <c r="D25" s="242"/>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C23" s="234"/>
+      <c r="D23" s="237"/>
+    </row>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C24" s="234"/>
+      <c r="D24" s="237"/>
+    </row>
+    <row r="25" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="235"/>
+      <c r="D25" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6870,16 +6576,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="48"/>
       <c r="B1" s="49"/>
       <c r="C1" s="49"/>
@@ -6903,7 +6609,7 @@
       </c>
       <c r="O1" s="52"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="49"/>
       <c r="B2" s="51"/>
       <c r="C2" s="51"/>
@@ -6922,7 +6628,7 @@
       <c r="N2" s="49"/>
       <c r="O2" s="49"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="49"/>
       <c r="B3" s="51"/>
       <c r="C3" s="51"/>
@@ -6945,7 +6651,7 @@
       </c>
       <c r="O3" s="54"/>
     </row>
-    <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
@@ -6966,11 +6672,11 @@
       <c r="N4" s="49"/>
       <c r="O4" s="49"/>
     </row>
-    <row r="5" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="243" t="s">
+    <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="239" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="243" t="s">
+      <c r="B5" s="239" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="55" t="s">
@@ -6982,7 +6688,7 @@
       <c r="E5" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="243" t="s">
+      <c r="F5" s="239" t="s">
         <v>75</v>
       </c>
       <c r="G5" s="37" t="s">
@@ -7004,16 +6710,16 @@
         <v>29</v>
       </c>
       <c r="M5" s="41"/>
-      <c r="N5" s="243" t="s">
+      <c r="N5" s="239" t="s">
         <v>78</v>
       </c>
-      <c r="O5" s="243" t="s">
+      <c r="O5" s="239" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="244"/>
-      <c r="B6" s="244"/>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="240"/>
+      <c r="B6" s="240"/>
       <c r="C6" s="56" t="s">
         <v>80</v>
       </c>
@@ -7023,7 +6729,7 @@
       <c r="E6" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="244"/>
+      <c r="F6" s="240"/>
       <c r="G6" s="44" t="s">
         <v>81</v>
       </c>
@@ -7043,10 +6749,10 @@
         <v>84</v>
       </c>
       <c r="M6" s="47"/>
-      <c r="N6" s="244"/>
-      <c r="O6" s="244"/>
-    </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N6" s="240"/>
+      <c r="O6" s="240"/>
+    </row>
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15">
         <v>1</v>
       </c>
@@ -7092,7 +6798,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
         <v>2</v>
       </c>
@@ -7138,7 +6844,7 @@
         <v>12569.682901267399</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15">
         <v>3</v>
       </c>
@@ -7184,7 +6890,7 @@
         <v>9919.7751374005984</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
         <v>4</v>
       </c>
@@ -7230,7 +6936,7 @@
         <v>14159.627559587479</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15">
         <v>5</v>
       </c>
@@ -7276,7 +6982,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <v>6</v>
       </c>
@@ -7322,7 +7028,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15">
         <v>7</v>
       </c>
@@ -7368,7 +7074,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15">
         <v>8</v>
       </c>
@@ -7414,7 +7120,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15">
         <v>9</v>
       </c>
@@ -7460,7 +7166,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15">
         <v>10</v>
       </c>
@@ -7506,7 +7212,7 @@
         <v>13629.64600681412</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15">
         <v>11</v>
       </c>
@@ -7552,7 +7258,7 @@
         <v>13099.66445404076</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15">
         <v>12</v>
       </c>
@@ -7598,7 +7304,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="15">
         <v>13</v>
       </c>
@@ -7644,7 +7350,7 @@
         <v>12569.682901267399</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15">
         <v>14</v>
       </c>
@@ -7690,7 +7396,7 @@
         <v>9919.7751374005984</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="15">
         <v>15</v>
       </c>
@@ -7736,7 +7442,7 @@
         <v>14159.627559587479</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15">
         <v>16</v>
       </c>
@@ -7782,7 +7488,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="15">
         <v>17</v>
       </c>
@@ -7828,7 +7534,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15">
         <v>18</v>
       </c>
@@ -7874,7 +7580,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15">
         <v>19</v>
       </c>
@@ -7920,7 +7626,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15">
         <v>20</v>
       </c>
@@ -7966,7 +7672,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15">
         <v>21</v>
       </c>
@@ -8012,7 +7718,7 @@
         <v>13629.64600681412</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15">
         <v>22</v>
       </c>
@@ -8058,7 +7764,7 @@
         <v>13099.66445404076</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="15"/>
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
@@ -8075,7 +7781,7 @@
       <c r="N29" s="6"/>
       <c r="O29" s="6"/>
     </row>
-    <row r="30" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
       <c r="B30" s="14"/>
       <c r="C30" s="57">
@@ -8116,7 +7822,7 @@
         <v>264873.42966686888</v>
       </c>
     </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E33" s="33"/>
       <c r="F33" s="33"/>
     </row>
